--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675A64CC-3CDB-4B6A-BC34-02DEE7F5FDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A261B831-7AC8-4A55-A3D2-CBC26664A0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
     <sheet name="asset_code" sheetId="2" r:id="rId2"/>
-    <sheet name="income_code" sheetId="3" r:id="rId3"/>
+    <sheet name="filing_requirement_code" sheetId="4" r:id="rId3"/>
+    <sheet name="income_code" sheetId="3" r:id="rId4"/>
+    <sheet name="pf_filing_requirement_code" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>status_code</t>
   </si>
@@ -101,6 +103,72 @@
   </si>
   <si>
     <t>income_code_effective_date</t>
+  </si>
+  <si>
+    <t>filing_requirement_code</t>
+  </si>
+  <si>
+    <t>filing_requirement_code_definition</t>
+  </si>
+  <si>
+    <t>filing_requirement_code_effective_date</t>
+  </si>
+  <si>
+    <t>990 - Not required to file (all other)</t>
+  </si>
+  <si>
+    <t>990 (all other) or 990EZ return</t>
+  </si>
+  <si>
+    <t>990 - Required to file Form 990-N - Income less than $50,000 per year</t>
+  </si>
+  <si>
+    <t>990 - Group return</t>
+  </si>
+  <si>
+    <t>990 - Required to file Form 990-BL, Black Lung Trusts</t>
+  </si>
+  <si>
+    <t>990 - Not required to file (church)</t>
+  </si>
+  <si>
+    <t>990 - Government 501(c)(1)</t>
+  </si>
+  <si>
+    <t>990 - Not required to file (religious organization)</t>
+  </si>
+  <si>
+    <t>990 - Not required to file (instrumentalities of states or political subdivisions)</t>
+  </si>
+  <si>
+    <t>pf_filing_requirement_code</t>
+  </si>
+  <si>
+    <t>pf_filing_requirement_code_definition</t>
+  </si>
+  <si>
+    <t>pf_filing_requirement_code_description</t>
+  </si>
+  <si>
+    <t>pf_filing_requirement_code_effective_date</t>
+  </si>
+  <si>
+    <t>No 990-PF return</t>
+  </si>
+  <si>
+    <t>990-PF return</t>
+  </si>
+  <si>
+    <t>Return due 5 months or the 15th day of the 5th month after the end of the taxable year.</t>
+  </si>
+  <si>
+    <t>Revoked, required to file Form 990-PF and Form 1120.</t>
+  </si>
+  <si>
+    <t>Presumptive</t>
+  </si>
+  <si>
+    <t>No return due</t>
   </si>
 </sst>
 </file>
@@ -656,6 +724,126 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8C9601-88C1-4ACF-A4DB-1D9ED72BCB8C}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>20241213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0CDB35C-585B-4DD3-B01E-2ED46C16F7EF}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -784,4 +972,84 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0813D5-4CF6-451E-8856-3E71508FC2CF}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>20241213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F943B9F7-A4D6-4DBE-A5B7-AB3636CD145D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6569F1-4400-4902-AD61-11DF37067A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="16440" windowHeight="28320" firstSheet="5" activeTab="5" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="ntee_code" sheetId="6" r:id="rId6"/>
     <sheet name="ntee_code_activity_type" sheetId="7" r:id="rId7"/>
     <sheet name="ntee_code_major_group" sheetId="8" r:id="rId8"/>
+    <sheet name="parent_organization" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1552">
   <si>
     <t>status_code</t>
   </si>
@@ -3757,6 +3758,948 @@
   </si>
   <si>
     <t>UNDEFINED</t>
+  </si>
+  <si>
+    <t>Air Line Dispatchers Association</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t>Air Line Pilots Association; International</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>Allied and Technical Workers District 50 International Union</t>
+  </si>
+  <si>
+    <t>ATW-50</t>
+  </si>
+  <si>
+    <t>Allied Industrial Workers of America International Union</t>
+  </si>
+  <si>
+    <t>AIWA</t>
+  </si>
+  <si>
+    <t>Aluminum Workers International Union</t>
+  </si>
+  <si>
+    <t>AWU</t>
+  </si>
+  <si>
+    <t>Amalgamated clothing Workers of America</t>
+  </si>
+  <si>
+    <t>ACW</t>
+  </si>
+  <si>
+    <t>Amalgamated Meat cutters &amp; Butcher Workmen of North America</t>
+  </si>
+  <si>
+    <t>MCBW</t>
+  </si>
+  <si>
+    <t>Amalgamated Transit Unit (F/K/A SERE)</t>
+  </si>
+  <si>
+    <t>ATU</t>
+  </si>
+  <si>
+    <t>Amalgamated Transit Union Women’s International Auxiliary</t>
+  </si>
+  <si>
+    <t>ATU-Aux</t>
+  </si>
+  <si>
+    <t>American Communications Association (Ind.)</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>American Federation of Government Employees</t>
+  </si>
+  <si>
+    <t>AFGE</t>
+  </si>
+  <si>
+    <t>American Federation of Grain Millers</t>
+  </si>
+  <si>
+    <t>AFGM</t>
+  </si>
+  <si>
+    <t>American Federation of Labor and Congress of Industrial Organizations</t>
+  </si>
+  <si>
+    <t>AFL-CIO</t>
+  </si>
+  <si>
+    <t>American Federation of Labor and Congress of Industrial Organizations — Auxiliaries</t>
+  </si>
+  <si>
+    <t>AFL-CIO Aux</t>
+  </si>
+  <si>
+    <t>American Federation of Musicians of the U.S. and Canada</t>
+  </si>
+  <si>
+    <t>AFM</t>
+  </si>
+  <si>
+    <t>American Federation of State, County and Municipal Employees</t>
+  </si>
+  <si>
+    <t>SCME</t>
+  </si>
+  <si>
+    <t>American Federation of Teachers</t>
+  </si>
+  <si>
+    <t>AFT</t>
+  </si>
+  <si>
+    <t>American Federation of Technical Engineers</t>
+  </si>
+  <si>
+    <t>FTE</t>
+  </si>
+  <si>
+    <t>American Flint Glass Workers Union of North American</t>
+  </si>
+  <si>
+    <t>FGWU</t>
+  </si>
+  <si>
+    <t>American Newspaper Guild</t>
+  </si>
+  <si>
+    <t>ANG</t>
+  </si>
+  <si>
+    <t>American Railway Supervisors</t>
+  </si>
+  <si>
+    <t>ARS</t>
+  </si>
+  <si>
+    <t>Bakery and Confectionery Workers’ International Union of America</t>
+  </si>
+  <si>
+    <t>BCWI</t>
+  </si>
+  <si>
+    <t>Bill Posters, Billers and Distributors of the U.S. and Canada International Alliance</t>
+  </si>
+  <si>
+    <t>BPBD</t>
+  </si>
+  <si>
+    <t>Boot &amp; Shoe Workers Union</t>
+  </si>
+  <si>
+    <t>BSWU</t>
+  </si>
+  <si>
+    <t>Bricklayers, Masons and Plasterers’ International Union of America</t>
+  </si>
+  <si>
+    <t>BMPI</t>
+  </si>
+  <si>
+    <t>Brotherhood of Locomotive Engineers</t>
+  </si>
+  <si>
+    <t>BLE</t>
+  </si>
+  <si>
+    <t>Brotherhood of Locomotive Engineers Auxiliary</t>
+  </si>
+  <si>
+    <t>BLE-Aux</t>
+  </si>
+  <si>
+    <t>Brotherhood of Maintenance of Way Employees</t>
+  </si>
+  <si>
+    <t>BMWE</t>
+  </si>
+  <si>
+    <t>Brotherhood of Maintenance of Way Employees Ladies Auxiliaries</t>
+  </si>
+  <si>
+    <t>BMWE-Aux</t>
+  </si>
+  <si>
+    <t>Brotherhood of Railroad Signalmen</t>
+  </si>
+  <si>
+    <t>BRS</t>
+  </si>
+  <si>
+    <t>Brotherhood of Railway, Airline and Steamship Clerks, Freight Handlers</t>
+  </si>
+  <si>
+    <t>BRAC</t>
+  </si>
+  <si>
+    <t>Brotherhood of Railway Carmen of America</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Brotherhood of Shoe and Allied Craftsmen</t>
+  </si>
+  <si>
+    <t>NSAC</t>
+  </si>
+  <si>
+    <t>Brotherhood of Sleeping Car Porters, Train Chair Car Coach Porters &amp; Attend.</t>
+  </si>
+  <si>
+    <t>SCP</t>
+  </si>
+  <si>
+    <t>Brotherhood of Utility Workers of New England</t>
+  </si>
+  <si>
+    <t>UWNE</t>
+  </si>
+  <si>
+    <t>Christian Labor Association of the United States of America (Ind.)</t>
+  </si>
+  <si>
+    <t>CLA</t>
+  </si>
+  <si>
+    <t>Cigar Maker’s International Union of America</t>
+  </si>
+  <si>
+    <t>CIUA</t>
+  </si>
+  <si>
+    <t>Communication Workers of America</t>
+  </si>
+  <si>
+    <t>CWA</t>
+  </si>
+  <si>
+    <t>Cooper’s International Union of North America</t>
+  </si>
+  <si>
+    <t>CIU</t>
+  </si>
+  <si>
+    <t>Cordova District Fisheries Union</t>
+  </si>
+  <si>
+    <t>CDFU</t>
+  </si>
+  <si>
+    <t>Distillery, Rectifying, Wine and Allied Workers International Union</t>
+  </si>
+  <si>
+    <t>DWAW</t>
+  </si>
+  <si>
+    <t>Flight Engineers’ International Association</t>
+  </si>
+  <si>
+    <t>FEIA</t>
+  </si>
+  <si>
+    <t>Glass Bottle Blowers Association of the U.S. and Canada</t>
+  </si>
+  <si>
+    <t>GBBA</t>
+  </si>
+  <si>
+    <t>Granite Cutter’s International Association of America</t>
+  </si>
+  <si>
+    <t>GCIA</t>
+  </si>
+  <si>
+    <t>Hotel and Restaurant Employees’ and Bartenders International Union</t>
+  </si>
+  <si>
+    <t>HREU</t>
+  </si>
+  <si>
+    <t>Independent Watchmen’s Association</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Insurance Workers International Union</t>
+  </si>
+  <si>
+    <t>IWIU</t>
+  </si>
+  <si>
+    <t>International Alliance of Theatrical State Employees &amp; Moving Picture Operators</t>
+  </si>
+  <si>
+    <t>LATSE</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters</t>
+  </si>
+  <si>
+    <t>LAFF</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters Auxiliary</t>
+  </si>
+  <si>
+    <t>LAFF-Aux</t>
+  </si>
+  <si>
+    <t>International Association of Heat and Frost Insulators &amp; Asbestos Workers</t>
+  </si>
+  <si>
+    <t>AWIA</t>
+  </si>
+  <si>
+    <t>International Association of Machinists &amp; Aerospace Workers</t>
+  </si>
+  <si>
+    <t>LAM</t>
+  </si>
+  <si>
+    <t>International Association of Marble, Slate &amp; Stone Polishers, etc.</t>
+  </si>
+  <si>
+    <t>MSSP</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Boilermakers, Iron Ship Builders, Blacksmiths</t>
+  </si>
+  <si>
+    <t>BMIS</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Electrical Workers</t>
+  </si>
+  <si>
+    <t>IBEW</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Firemen and Oilers</t>
+  </si>
+  <si>
+    <t>FOIB</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Painters and Allied Trades</t>
+  </si>
+  <si>
+    <t>BPAT</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Potters and Allied Workers</t>
+  </si>
+  <si>
+    <t>BOP</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Teamsters, Chauffeurs, Warehousemen &amp; Helpers of America (Ind.)</t>
+  </si>
+  <si>
+    <t>TCWH</t>
+  </si>
+  <si>
+    <t>International Chemical Workers Union</t>
+  </si>
+  <si>
+    <t>ICWU</t>
+  </si>
+  <si>
+    <t>International Die Sinker’s Conference</t>
+  </si>
+  <si>
+    <t>DSC</t>
+  </si>
+  <si>
+    <t>International Guards Union of America</t>
+  </si>
+  <si>
+    <t>GUA</t>
+  </si>
+  <si>
+    <t>International Jewelry Workers Union</t>
+  </si>
+  <si>
+    <t>IJWU</t>
+  </si>
+  <si>
+    <t>International Ladies Garment Workers Union</t>
+  </si>
+  <si>
+    <t>ILGW</t>
+  </si>
+  <si>
+    <t>International Leather Goods, Plastic &amp; Novelty Workers Union</t>
+  </si>
+  <si>
+    <t>LGPW</t>
+  </si>
+  <si>
+    <t>International Longshoremen’s and Warehousemen’s Union</t>
+  </si>
+  <si>
+    <t>ILWU</t>
+  </si>
+  <si>
+    <t>International Longshoremens Association (Ind.)</t>
+  </si>
+  <si>
+    <t>ILA</t>
+  </si>
+  <si>
+    <t>International McClass Sailboat Racing Association (Ind.)</t>
+  </si>
+  <si>
+    <t>IMCCSRA</t>
+  </si>
+  <si>
+    <t>International Mailers Union</t>
+  </si>
+  <si>
+    <t>IMU</t>
+  </si>
+  <si>
+    <t>International Molders &amp; Allied Workers Union</t>
+  </si>
+  <si>
+    <t>MAWU</t>
+  </si>
+  <si>
+    <t>International Organization of Masters, Mates &amp; Pilots</t>
+  </si>
+  <si>
+    <t>MMPI</t>
+  </si>
+  <si>
+    <t>International Plate Printers, Die Stampers &amp; Engravers Union of North America</t>
+  </si>
+  <si>
+    <t>PPEU</t>
+  </si>
+  <si>
+    <t>International Printing Pressmen &amp; Assistants Union of North America</t>
+  </si>
+  <si>
+    <t>IPP</t>
+  </si>
+  <si>
+    <t>International Stereotypers &amp; Electrotypes Union of North America</t>
+  </si>
+  <si>
+    <t>ISEU</t>
+  </si>
+  <si>
+    <t>International Typographical Union of North America</t>
+  </si>
+  <si>
+    <t>ITU</t>
+  </si>
+  <si>
+    <t>International Union of Electrical Radio and Machine Workers</t>
+  </si>
+  <si>
+    <t>IUE</t>
+  </si>
+  <si>
+    <t>International Union of Elevator Constructors</t>
+  </si>
+  <si>
+    <t>ECI</t>
+  </si>
+  <si>
+    <t>International Union of Journeymen Horseshoers of the U.S. and Canada</t>
+  </si>
+  <si>
+    <t>HSIU</t>
+  </si>
+  <si>
+    <t>International Union of Life Insurance Agents</t>
+  </si>
+  <si>
+    <t>LIA</t>
+  </si>
+  <si>
+    <t>International Union of United Brewery, Flour Cereal, Soft Drinks and Distillery Workers of America</t>
+  </si>
+  <si>
+    <t>BSDW</t>
+  </si>
+  <si>
+    <t>International Woodworkers of America</t>
+  </si>
+  <si>
+    <t>IWA</t>
+  </si>
+  <si>
+    <t>Journeymen Barbers, Hairdressers, Cosmetologists &amp; Proprietors A/K/A Barbers, Beauticians &amp; Allied Industries</t>
+  </si>
+  <si>
+    <t>BHCI/BBAI</t>
+  </si>
+  <si>
+    <t>Laborers International Union of North America</t>
+  </si>
+  <si>
+    <t>HCL</t>
+  </si>
+  <si>
+    <t>Laundry &amp; Dry Cleaning Workers International Union</t>
+  </si>
+  <si>
+    <t>LDCI</t>
+  </si>
+  <si>
+    <t>Laundry &amp; Dry Cleaning Workers International Union (Ind.)</t>
+  </si>
+  <si>
+    <t>LWIU</t>
+  </si>
+  <si>
+    <t>Leather Workers International Union of America</t>
+  </si>
+  <si>
+    <t>LWIUA</t>
+  </si>
+  <si>
+    <t>Marine &amp; Shipbuilding Workers of America, Industrial Union</t>
+  </si>
+  <si>
+    <t>MSWA</t>
+  </si>
+  <si>
+    <t>Metal Polishers, Buffers, Platers &amp; Helpers International Union</t>
+  </si>
+  <si>
+    <t>MPBP</t>
+  </si>
+  <si>
+    <t>National Alliance of Postal &amp; Federal Employees (F/K/A NAPE)</t>
+  </si>
+  <si>
+    <t>NAPFE</t>
+  </si>
+  <si>
+    <t>National Association of Broadcast Employees &amp; Technicians</t>
+  </si>
+  <si>
+    <t>NABET</t>
+  </si>
+  <si>
+    <t>National Association of Government Employees (Ind.)</t>
+  </si>
+  <si>
+    <t>NAGE</t>
+  </si>
+  <si>
+    <t>National Association of Letter Carriers of the U.S.A.</t>
+  </si>
+  <si>
+    <t>NALC</t>
+  </si>
+  <si>
+    <t>National Association of Post Office Mail Handlers, Messengers and Group Leaders</t>
+  </si>
+  <si>
+    <t>POMH</t>
+  </si>
+  <si>
+    <t>National Congress of Industrial Waterproofing &amp; Misc. Workers of America (Ind.)</t>
+  </si>
+  <si>
+    <t>NCIWMWA</t>
+  </si>
+  <si>
+    <t>National Federation of Federal Employees (Ind.)</t>
+  </si>
+  <si>
+    <t>NFFE</t>
+  </si>
+  <si>
+    <t>National League of Postmasters of the U.S. (Ind.)</t>
+  </si>
+  <si>
+    <t>NLP</t>
+  </si>
+  <si>
+    <t>National Marine Engineers Beneficial Assn. Of the U.S.A.</t>
+  </si>
+  <si>
+    <t>MEBA</t>
+  </si>
+  <si>
+    <t>National Rural Letter Carriers’ Association (Ind.)</t>
+  </si>
+  <si>
+    <t>RLCA</t>
+  </si>
+  <si>
+    <t>National Treasury Employees Union (F/K/A NAIRE) (Ind.)</t>
+  </si>
+  <si>
+    <t>NTEU</t>
+  </si>
+  <si>
+    <t>Office &amp; Professional Employees International Union</t>
+  </si>
+  <si>
+    <t>OEIU</t>
+  </si>
+  <si>
+    <t>Oil, Chemical &amp; Atomic Workers International Union</t>
+  </si>
+  <si>
+    <t>OCAW</t>
+  </si>
+  <si>
+    <t>Operative Plasterer’s &amp; Cement Masons International Association</t>
+  </si>
+  <si>
+    <t>PCM</t>
+  </si>
+  <si>
+    <t>Pattern Makers’ League of North America</t>
+  </si>
+  <si>
+    <t>PML</t>
+  </si>
+  <si>
+    <t>Railroad Yardmasters of America</t>
+  </si>
+  <si>
+    <t>RYA</t>
+  </si>
+  <si>
+    <t>Railway Patrolmen’s International Union</t>
+  </si>
+  <si>
+    <t>IURP</t>
+  </si>
+  <si>
+    <t>Retail Clerks International Association</t>
+  </si>
+  <si>
+    <t>RCIA</t>
+  </si>
+  <si>
+    <t>Retail, Wholesale &amp; Department Store Union</t>
+  </si>
+  <si>
+    <t>RWDS</t>
+  </si>
+  <si>
+    <t>Seafarers’ International Union of North America</t>
+  </si>
+  <si>
+    <t>SIU</t>
+  </si>
+  <si>
+    <t>Service Employees International Union (F/K/A DSE)</t>
+  </si>
+  <si>
+    <t>SEIU</t>
+  </si>
+  <si>
+    <t>Sheet Metal Workers International Association</t>
+  </si>
+  <si>
+    <t>SMW</t>
+  </si>
+  <si>
+    <t>Stove, Furnace &amp; Allied Appliance Workers International Union of North America</t>
+  </si>
+  <si>
+    <t>SFAW</t>
+  </si>
+  <si>
+    <t>Textile Workers Union of America</t>
+  </si>
+  <si>
+    <t>TWUA</t>
+  </si>
+  <si>
+    <t>Tobacco Workers International Union</t>
+  </si>
+  <si>
+    <t>TWIU</t>
+  </si>
+  <si>
+    <t>Transport Workers Union of America</t>
+  </si>
+  <si>
+    <t>TWU</t>
+  </si>
+  <si>
+    <t>United Association of Journeymen &amp; Apprentices of the Plumbing &amp; Pipe Fitting Industry</t>
+  </si>
+  <si>
+    <t>PPF</t>
+  </si>
+  <si>
+    <t>United Automobile, Aerospace &amp; Agricultural Workers of America</t>
+  </si>
+  <si>
+    <t>UAW</t>
+  </si>
+  <si>
+    <t>United Brick &amp; Clay Workers of America</t>
+  </si>
+  <si>
+    <t>BCW</t>
+  </si>
+  <si>
+    <t>United Brotherhood of Carpenters &amp; Joiners of America</t>
+  </si>
+  <si>
+    <t>BCJ</t>
+  </si>
+  <si>
+    <t>United Cement, Lime &amp; Gypsum Workers International Union</t>
+  </si>
+  <si>
+    <t>CLGW</t>
+  </si>
+  <si>
+    <t>United Electrical, Radio &amp; Machine Workers of Americ (Ind.)</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>United Furniture Workers of America</t>
+  </si>
+  <si>
+    <t>FWA</t>
+  </si>
+  <si>
+    <t>United Garment Workers of America</t>
+  </si>
+  <si>
+    <t>UGWA</t>
+  </si>
+  <si>
+    <t>United Glass &amp; Ceramic Workers of North America</t>
+  </si>
+  <si>
+    <t>GCW</t>
+  </si>
+  <si>
+    <t>United Hatters Cap &amp; Military Workers International Union</t>
+  </si>
+  <si>
+    <t>HCMW</t>
+  </si>
+  <si>
+    <t>United Mine Workers of America (Ind.)</t>
+  </si>
+  <si>
+    <t>UMW</t>
+  </si>
+  <si>
+    <t>United Paperworkers International Union (from the merger of PMPW &amp; PSPM)</t>
+  </si>
+  <si>
+    <t>UPIU</t>
+  </si>
+  <si>
+    <t>United Plant Guard Workers of America (Ind.)</t>
+  </si>
+  <si>
+    <t>PGW</t>
+  </si>
+  <si>
+    <t>United Rubber, Cork, Linoleum &amp; Plastic Workers of America</t>
+  </si>
+  <si>
+    <t>RWA</t>
+  </si>
+  <si>
+    <t>United Shoe Workers of America</t>
+  </si>
+  <si>
+    <t>SWA</t>
+  </si>
+  <si>
+    <t>United Slate, Tile &amp; Composition Roofers, Damp &amp; Waterproof Workers of Assn.</t>
+  </si>
+  <si>
+    <t>RDWA</t>
+  </si>
+  <si>
+    <t>United Steelworkers of America</t>
+  </si>
+  <si>
+    <t>USW</t>
+  </si>
+  <si>
+    <t>United Telegraph Workers</t>
+  </si>
+  <si>
+    <t>UTW</t>
+  </si>
+  <si>
+    <t>United Textile Workers of America</t>
+  </si>
+  <si>
+    <t>UTWA</t>
+  </si>
+  <si>
+    <t>United Transport Service Employees of American International Union</t>
+  </si>
+  <si>
+    <t>TSEA</t>
+  </si>
+  <si>
+    <t>United Transportation Union</t>
+  </si>
+  <si>
+    <t>UTU</t>
+  </si>
+  <si>
+    <t>Upholsterers’ International Union of N.A.</t>
+  </si>
+  <si>
+    <t>UIUA</t>
+  </si>
+  <si>
+    <t>Utilities Workers Union of America</t>
+  </si>
+  <si>
+    <t>UWUA</t>
+  </si>
+  <si>
+    <t>Window Glass Cutters League of America</t>
+  </si>
+  <si>
+    <t>GCLA</t>
+  </si>
+  <si>
+    <t>Wood, Wine &amp; Metal Lathers’ International Union</t>
+  </si>
+  <si>
+    <t>IUWM</t>
+  </si>
+  <si>
+    <t>American Association of University Women</t>
+  </si>
+  <si>
+    <t>AWARE</t>
+  </si>
+  <si>
+    <t>American Medical Association</t>
+  </si>
+  <si>
+    <t>AMA</t>
+  </si>
+  <si>
+    <t>American Veterans of World War II</t>
+  </si>
+  <si>
+    <t>AM VETS</t>
+  </si>
+  <si>
+    <t>Benevolent and Protective Order of Elks</t>
+  </si>
+  <si>
+    <t>BP OE</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>Camp Fire Girls</t>
+  </si>
+  <si>
+    <t>CFC</t>
+  </si>
+  <si>
+    <t>Daughters of the American Revolution</t>
+  </si>
+  <si>
+    <t>DAR</t>
+  </si>
+  <si>
+    <t>Disabled American Veterans</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>Future Farmers of America</t>
+  </si>
+  <si>
+    <t>FF A</t>
+  </si>
+  <si>
+    <t>Girl Scouts of America</t>
+  </si>
+  <si>
+    <t>GSA</t>
+  </si>
+  <si>
+    <t>Knights of Columbus</t>
+  </si>
+  <si>
+    <t>KC</t>
+  </si>
+  <si>
+    <t>National Association for the Advancement of Colored People</t>
+  </si>
+  <si>
+    <t>NAACP</t>
+  </si>
+  <si>
+    <t>Parents Teachers Association</t>
+  </si>
+  <si>
+    <t>Society for the Preservation and Encouragement of Barbershop Quartet Singing of America</t>
+  </si>
+  <si>
+    <t>SPOUSED</t>
+  </si>
+  <si>
+    <t>Veterans of Foreign Wars</t>
+  </si>
+  <si>
+    <t>VFW</t>
+  </si>
+  <si>
+    <t>Young Men’s Christian Association</t>
+  </si>
+  <si>
+    <t>YMCA</t>
+  </si>
+  <si>
+    <t>Young Women’s Christian Association</t>
+  </si>
+  <si>
+    <t>YWCA</t>
+  </si>
+  <si>
+    <t>parent_org_name</t>
+  </si>
+  <si>
+    <t>abbreviation</t>
+  </si>
+  <si>
+    <t>gen</t>
+  </si>
+  <si>
+    <t>PTA</t>
   </si>
 </sst>
 </file>
@@ -3766,8 +4709,16 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -3783,7 +4734,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -3791,14 +4742,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14084,4 +15102,1724 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C13D203-B39D-4F56-8E03-8D481588AEBE}">
+  <dimension ref="A1:C157"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C4" s="7">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C5" s="7">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C7" s="7">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C8" s="7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C9" s="7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C10" s="7">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C11" s="7">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C12" s="7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C16" s="7">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C18" s="7">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C19" s="7">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C20" s="7">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C21" s="7">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C22" s="7">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C23" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C25" s="7">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C26" s="7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C27" s="7">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C28" s="7">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C29" s="7">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C30" s="7">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C31" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C32" s="7">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C33" s="7">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C34" s="7">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C35" s="7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C36" s="7">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C38" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C40" s="7">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C44" s="7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C45" s="7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C46" s="7">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C49" s="7">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C50" s="7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C52" s="7">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C53" s="7">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C54" s="7">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C56" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C57" s="7">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C58" s="7">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C59" s="7">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C60" s="7">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C61" s="7">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C62" s="7">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C64" s="7">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C65" s="7">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C66" s="7">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C67" s="7">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C68" s="7">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C69" s="7">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C70" s="7">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C71" s="7">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C72" s="7">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C73" s="7">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C74" s="7">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C75" s="7">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C76" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C78" s="7">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C79" s="7">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C80" s="7">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C81" s="7">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C82" s="7">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C83" s="7"/>
+    </row>
+    <row r="84" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C84" s="7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C86" s="7">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C88" s="7">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C89" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C90" s="7">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="6" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="6" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C92" s="7">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C93" s="7">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C94" s="7">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C95" s="7">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="6" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C96" s="7">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C97" s="7">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C98" s="7">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C99" s="7">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C100" s="7">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C101" s="7">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="6" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C102" s="7">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C103" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C104" s="7">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C105" s="7">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C106" s="7">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C107" s="7">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C108" s="7">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="6" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C109" s="7">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="6" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C110" s="7">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="6" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C111" s="7">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C112" s="7">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="6" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C113" s="7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C114" s="7">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="6" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C115" s="7">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C116" s="7">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="6" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C117" s="7">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C118" s="7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="6" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C119" s="7">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C120" s="7">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C121" s="7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="6" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C122" s="7">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="6" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C123" s="7">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="6" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C124" s="7">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="6" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C125" s="7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C126" s="7"/>
+    </row>
+    <row r="127" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="6" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C127" s="7">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C128" s="7">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C129" s="7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="6" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C130" s="7">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C131" s="7">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="6" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C132" s="7">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C133" s="7">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="6" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C134" s="7">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C135" s="7">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="6" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C136" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="6" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C137" s="7">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="6" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C138" s="7">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="6" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C139" s="7">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C140" s="7">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="6" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C141" s="7">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="6" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C142" s="7"/>
+    </row>
+    <row r="143" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="6" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C143" s="7">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C144" s="7">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C145" s="7">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="6" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C146" s="7">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C147" s="7">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="6" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C148" s="7">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="6" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C149" s="7">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C150" s="7"/>
+    </row>
+    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="6" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C151" s="7">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C152" s="7">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="6" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C153" s="7"/>
+    </row>
+    <row r="154" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="6" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C154" s="7">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="6" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C155" s="7"/>
+    </row>
+    <row r="156" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C156" s="7"/>
+    </row>
+    <row r="157" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C157" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6569F1-4400-4902-AD61-11DF37067A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D53A0F3-E5E7-493F-BFE0-18DC2F79B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="9" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ntee_code_activity_type" sheetId="7" r:id="rId7"/>
     <sheet name="ntee_code_major_group" sheetId="8" r:id="rId8"/>
     <sheet name="parent_organization" sheetId="9" r:id="rId9"/>
+    <sheet name="subsection_classification_code" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1656">
   <si>
     <t>status_code</t>
   </si>
@@ -4700,6 +4701,318 @@
   </si>
   <si>
     <t>PTA</t>
+  </si>
+  <si>
+    <t>subsection_code</t>
+  </si>
+  <si>
+    <t>classification_code</t>
+  </si>
+  <si>
+    <t>classification_description</t>
+  </si>
+  <si>
+    <t>exempt_organization_type</t>
+  </si>
+  <si>
+    <t>effective_start_date</t>
+  </si>
+  <si>
+    <t>effective_end_date</t>
+  </si>
+  <si>
+    <t>Government instrumentality</t>
+  </si>
+  <si>
+    <t>501(c)(1)</t>
+  </si>
+  <si>
+    <t>Title-holding corporation</t>
+  </si>
+  <si>
+    <t>501(c)(2)</t>
+  </si>
+  <si>
+    <t>Charitable Organization</t>
+  </si>
+  <si>
+    <t>501(c)(3)</t>
+  </si>
+  <si>
+    <t>Educational organization</t>
+  </si>
+  <si>
+    <t>Literary organization</t>
+  </si>
+  <si>
+    <t>Organization to prevent cruelty to animals</t>
+  </si>
+  <si>
+    <t>Organization to prevent cruelty to children</t>
+  </si>
+  <si>
+    <t>Organization for public safety testing</t>
+  </si>
+  <si>
+    <t>Religious organization</t>
+  </si>
+  <si>
+    <t>Scientific organization</t>
+  </si>
+  <si>
+    <t>Civic league</t>
+  </si>
+  <si>
+    <t>501(c)(4)</t>
+  </si>
+  <si>
+    <t>Local association of employees</t>
+  </si>
+  <si>
+    <t>Social welfare organization</t>
+  </si>
+  <si>
+    <t>Agriculture organization</t>
+  </si>
+  <si>
+    <t>501(c)(5)</t>
+  </si>
+  <si>
+    <t>Horticulture organization</t>
+  </si>
+  <si>
+    <t>Labor organization</t>
+  </si>
+  <si>
+    <t>Board of Trade</t>
+  </si>
+  <si>
+    <t>501(c)(6)</t>
+  </si>
+  <si>
+    <t>Business league</t>
+  </si>
+  <si>
+    <t>Chamber of Commerce</t>
+  </si>
+  <si>
+    <t>Real estate board</t>
+  </si>
+  <si>
+    <t>Pleasure, recreational, or social club</t>
+  </si>
+  <si>
+    <t>501(c)(7)</t>
+  </si>
+  <si>
+    <t>Fraternal beneficiary society, order or association</t>
+  </si>
+  <si>
+    <t>501(c)(8)</t>
+  </si>
+  <si>
+    <t>Voluntary employees’ beneficiary association (Non-government)</t>
+  </si>
+  <si>
+    <t>501(c)(9)</t>
+  </si>
+  <si>
+    <t>Voluntary employees’ beneficiary association (Government emp.’s)</t>
+  </si>
+  <si>
+    <t>Domestic fraternal societies and associations</t>
+  </si>
+  <si>
+    <t>501(c)(10)</t>
+  </si>
+  <si>
+    <t>Teachers’ retirement fund association</t>
+  </si>
+  <si>
+    <t>501(c)(11)</t>
+  </si>
+  <si>
+    <t>Benevolent life insurance association</t>
+  </si>
+  <si>
+    <t>501(c)(12)</t>
+  </si>
+  <si>
+    <t>Mutual ditch or irrigation company</t>
+  </si>
+  <si>
+    <t>Mutual or cooperative telephone company</t>
+  </si>
+  <si>
+    <t>Mutual electric company, mutual water company, etc.</t>
+  </si>
+  <si>
+    <t>Burial association</t>
+  </si>
+  <si>
+    <t>501(c)(13)</t>
+  </si>
+  <si>
+    <t>Cemetery company</t>
+  </si>
+  <si>
+    <t>Credit Union</t>
+  </si>
+  <si>
+    <t>501(c)(14)</t>
+  </si>
+  <si>
+    <t>Other mutual corporation or association</t>
+  </si>
+  <si>
+    <t>Mutual insurance company or association other than life or marine</t>
+  </si>
+  <si>
+    <t>501(c)(15)</t>
+  </si>
+  <si>
+    <t>Corporation financing crop operation</t>
+  </si>
+  <si>
+    <t>501(c)(16)</t>
+  </si>
+  <si>
+    <t>Supplemental unemployment compensation trust or plan</t>
+  </si>
+  <si>
+    <t>501(c)(17)</t>
+  </si>
+  <si>
+    <t>Employee funded pension trust (created before 6–25–59)</t>
+  </si>
+  <si>
+    <t>501(c)(18)</t>
+  </si>
+  <si>
+    <t>Post or organization of war veterans</t>
+  </si>
+  <si>
+    <t>501(c)(19)</t>
+  </si>
+  <si>
+    <t>Legal Services Organization</t>
+  </si>
+  <si>
+    <t>501(c)(20)</t>
+  </si>
+  <si>
+    <t>Black Lung</t>
+  </si>
+  <si>
+    <t>501(c)(21)</t>
+  </si>
+  <si>
+    <t>Multiemployer Pension Plan</t>
+  </si>
+  <si>
+    <t>501(c)(22)</t>
+  </si>
+  <si>
+    <t>Veterans Association Founded Prior to 1880</t>
+  </si>
+  <si>
+    <t>501(c)(23)</t>
+  </si>
+  <si>
+    <t>Trust described in Section 4049 of ERISA</t>
+  </si>
+  <si>
+    <t>501(c)(24)</t>
+  </si>
+  <si>
+    <t>Title Holding Corporation or Trust</t>
+  </si>
+  <si>
+    <t>501(c)(25)</t>
+  </si>
+  <si>
+    <t>State-sponsored High-Risk Health Insurance Org. Effective (1/1/99)</t>
+  </si>
+  <si>
+    <t>501(c)(26)</t>
+  </si>
+  <si>
+    <t>State-sponsored Worker’s Compensation Reinsurance Organization (Effective 1/1/99)</t>
+  </si>
+  <si>
+    <t>501(c)(27)</t>
+  </si>
+  <si>
+    <t>National Railroad Retirement Investment Trust Classification</t>
+  </si>
+  <si>
+    <t>501(c)(28)</t>
+  </si>
+  <si>
+    <t>Qualified non profit Health Insurance Issuers</t>
+  </si>
+  <si>
+    <t>501(c)(29)</t>
+  </si>
+  <si>
+    <t>Apostolic and religious organization</t>
+  </si>
+  <si>
+    <t>501(d)</t>
+  </si>
+  <si>
+    <t>Cooperative hospital service organization</t>
+  </si>
+  <si>
+    <t>501(e)</t>
+  </si>
+  <si>
+    <t>Cooperative service organizations of operating education org’s</t>
+  </si>
+  <si>
+    <t>501(f)</t>
+  </si>
+  <si>
+    <t>Child care under 501(k)</t>
+  </si>
+  <si>
+    <t>501(k)</t>
+  </si>
+  <si>
+    <t>Charitable Risk Pool (Effective 1/1/99)</t>
+  </si>
+  <si>
+    <t>501(n)</t>
+  </si>
+  <si>
+    <t>Farmers’ Cooperative</t>
+  </si>
+  <si>
+    <t>Qualified State-Sponsored Tuition Program</t>
+  </si>
+  <si>
+    <t>IRC 527</t>
+  </si>
+  <si>
+    <t>Non-exempt charitable trust 4947(a)(2) (Split Interest)</t>
+  </si>
+  <si>
+    <t>4947(a)(2)</t>
+  </si>
+  <si>
+    <t>Non-exempt charitable trust (Public Charity)</t>
+  </si>
+  <si>
+    <t>4947(a)(1)</t>
+  </si>
+  <si>
+    <t>Non-exempt charitable trust (Trust treated as Private Foundation)</t>
+  </si>
+  <si>
+    <t>Taxable Farmer’s Cooperative</t>
+  </si>
+  <si>
+    <t>1381(a)(2)</t>
   </si>
 </sst>
 </file>
@@ -5199,6 +5512,1256 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B298717-5B0C-43D8-96E1-9B90896F2A43}">
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E2">
+        <v>20241213</v>
+      </c>
+      <c r="F2">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E3">
+        <v>20241213</v>
+      </c>
+      <c r="F3">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E4">
+        <v>20241213</v>
+      </c>
+      <c r="F4">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E5">
+        <v>20241213</v>
+      </c>
+      <c r="F5">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E6">
+        <v>20241213</v>
+      </c>
+      <c r="F6">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E7">
+        <v>20241213</v>
+      </c>
+      <c r="F7">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E8">
+        <v>20241213</v>
+      </c>
+      <c r="F8">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E9">
+        <v>20241213</v>
+      </c>
+      <c r="F9">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E10">
+        <v>20241213</v>
+      </c>
+      <c r="F10">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E11">
+        <v>20241213</v>
+      </c>
+      <c r="F11">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E12">
+        <v>20241213</v>
+      </c>
+      <c r="F12">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E13">
+        <v>20241213</v>
+      </c>
+      <c r="F13">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E14">
+        <v>20241213</v>
+      </c>
+      <c r="F14">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E15">
+        <v>20241213</v>
+      </c>
+      <c r="F15">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E16">
+        <v>20241213</v>
+      </c>
+      <c r="F16">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E17">
+        <v>20241213</v>
+      </c>
+      <c r="F17">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E18">
+        <v>20241213</v>
+      </c>
+      <c r="F18">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E19">
+        <v>20241213</v>
+      </c>
+      <c r="F19">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E20">
+        <v>20241213</v>
+      </c>
+      <c r="F20">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E21">
+        <v>20241213</v>
+      </c>
+      <c r="F21">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E22">
+        <v>20241213</v>
+      </c>
+      <c r="F22">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E23">
+        <v>20241213</v>
+      </c>
+      <c r="F23">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E24">
+        <v>20241213</v>
+      </c>
+      <c r="F24">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E25">
+        <v>20241213</v>
+      </c>
+      <c r="F25">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E26">
+        <v>20241213</v>
+      </c>
+      <c r="F26">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E27">
+        <v>20241213</v>
+      </c>
+      <c r="F27">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E28">
+        <v>20241213</v>
+      </c>
+      <c r="F28">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>12</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E29">
+        <v>20241213</v>
+      </c>
+      <c r="F29">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>12</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E30">
+        <v>20241213</v>
+      </c>
+      <c r="F30">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>12</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E31">
+        <v>20241213</v>
+      </c>
+      <c r="F31">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>13</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E32">
+        <v>20241213</v>
+      </c>
+      <c r="F32">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>13</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E33">
+        <v>20241213</v>
+      </c>
+      <c r="F33">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>14</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E34">
+        <v>20241213</v>
+      </c>
+      <c r="F34">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>14</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E35">
+        <v>20241213</v>
+      </c>
+      <c r="F35">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>15</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E36">
+        <v>20241213</v>
+      </c>
+      <c r="F36">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>16</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E37">
+        <v>20241213</v>
+      </c>
+      <c r="F37">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E38">
+        <v>20241213</v>
+      </c>
+      <c r="F38">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E39">
+        <v>20241213</v>
+      </c>
+      <c r="F39">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E40">
+        <v>20241213</v>
+      </c>
+      <c r="F40">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>20</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E41">
+        <v>20241213</v>
+      </c>
+      <c r="F41">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>21</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E42">
+        <v>20241213</v>
+      </c>
+      <c r="F42">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>22</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E43">
+        <v>20241213</v>
+      </c>
+      <c r="F43">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>23</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E44">
+        <v>20241213</v>
+      </c>
+      <c r="F44">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E45">
+        <v>20241213</v>
+      </c>
+      <c r="F45">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>25</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E46">
+        <v>20241213</v>
+      </c>
+      <c r="F46">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>26</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E47">
+        <v>20241213</v>
+      </c>
+      <c r="F47">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>27</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E48">
+        <v>20241213</v>
+      </c>
+      <c r="F48">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>28</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E49">
+        <v>20241213</v>
+      </c>
+      <c r="F49">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>29</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E50">
+        <v>20241213</v>
+      </c>
+      <c r="F50">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E51">
+        <v>20241213</v>
+      </c>
+      <c r="F51">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E52">
+        <v>20241213</v>
+      </c>
+      <c r="F52">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>60</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E53">
+        <v>20241213</v>
+      </c>
+      <c r="F53">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>70</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E54">
+        <v>20241213</v>
+      </c>
+      <c r="F54">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>71</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E55">
+        <v>20241213</v>
+      </c>
+      <c r="F55">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>80</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D56">
+        <v>521</v>
+      </c>
+      <c r="E56">
+        <v>20241213</v>
+      </c>
+      <c r="F56">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>81</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D57">
+        <v>529</v>
+      </c>
+      <c r="E57">
+        <v>20241213</v>
+      </c>
+      <c r="F57">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>82</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D58">
+        <v>82</v>
+      </c>
+      <c r="E58">
+        <v>20241213</v>
+      </c>
+      <c r="F58">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>90</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E59">
+        <v>20241213</v>
+      </c>
+      <c r="F59">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>91</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E60">
+        <v>20241213</v>
+      </c>
+      <c r="F60">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>92</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E61">
+        <v>20241213</v>
+      </c>
+      <c r="F61">
+        <v>99991231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>93</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E62">
+        <v>20241213</v>
+      </c>
+      <c r="F62">
+        <v>99991231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F26964-D323-4807-93C3-4339F47CA786}">
   <dimension ref="A1:C11"/>

--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D53A0F3-E5E7-493F-BFE0-18DC2F79B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E71EF2-EBC7-4F5E-A034-7453DB528E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="9" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="ntee_code_major_group" sheetId="8" r:id="rId8"/>
     <sheet name="parent_organization" sheetId="9" r:id="rId9"/>
     <sheet name="subsection_classification_code" sheetId="10" r:id="rId10"/>
+    <sheet name="affiliation_code" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="1673">
   <si>
     <t>status_code</t>
   </si>
@@ -5013,6 +5014,63 @@
   </si>
   <si>
     <t>1381(a)(2)</t>
+  </si>
+  <si>
+    <t>affiliation_code</t>
+  </si>
+  <si>
+    <t>affiliation_code_definition</t>
+  </si>
+  <si>
+    <t>affiliation_code_description</t>
+  </si>
+  <si>
+    <t>Central Organization (Individual Ruling)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is a central type organization (no group exemption) of a National,_x000D_
+Regional or Geographic grouping of organizations.</t>
+  </si>
+  <si>
+    <t>Intermediate Organization (Individual Ruling)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is an intermediate organization (no group exemption) of a_x000D_
+National, Regional or Geographic grouping of organizations (such as a state headquarters of a national_x000D_
+organization).</t>
+  </si>
+  <si>
+    <t>Independent organization (Individual Ruling)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is an independent organization or an independent auxiliary_x000D_
+(i.e., not affiliated with a National, Regional, or Geographic grouping of organizations).</t>
+  </si>
+  <si>
+    <t>Parent of a group ruling (not a church)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is a parent (group ruling) and is not a church or 501(c)(1)_x000D_
+organization.</t>
+  </si>
+  <si>
+    <t>Intermediate parent (subordinate by state)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is a group exemption intermediate organization of a National,_x000D_
+Regional or Geographic grouping of organizations.</t>
+  </si>
+  <si>
+    <t>Parent of a church</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is a parent (group ruling) and is a church or 501(c)(1) organization.</t>
+  </si>
+  <si>
+    <t>Subordinate of a group ruling (also, group return)</t>
+  </si>
+  <si>
+    <t>This code is used if the organization is a subordinate in a group ruling.</t>
   </si>
 </sst>
 </file>
@@ -6762,6 +6820,104 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B295775B-C545-42EF-B1E6-C8444CDB5163}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F26964-D323-4807-93C3-4339F47CA786}">
   <dimension ref="A1:C11"/>

--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E71EF2-EBC7-4F5E-A034-7453DB528E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC1D010-B9D6-4E7E-9E65-567729AE50E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="11" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="parent_organization" sheetId="9" r:id="rId9"/>
     <sheet name="subsection_classification_code" sheetId="10" r:id="rId10"/>
     <sheet name="affiliation_code" sheetId="11" r:id="rId11"/>
+    <sheet name="deductibility_code" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="1673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1681">
   <si>
     <t>status_code</t>
   </si>
@@ -5071,6 +5072,30 @@
   </si>
   <si>
     <t>This code is used if the organization is a subordinate in a group ruling.</t>
+  </si>
+  <si>
+    <t>deductibility_code</t>
+  </si>
+  <si>
+    <t>deductibility_code_definition</t>
+  </si>
+  <si>
+    <t>deductibility_code_start_date</t>
+  </si>
+  <si>
+    <t>deductibility_code_end_date</t>
+  </si>
+  <si>
+    <t>Contributions are deductible</t>
+  </si>
+  <si>
+    <t>Contributions aren't deductible</t>
+  </si>
+  <si>
+    <t>Contributions are deductible under treaty provisions</t>
+  </si>
+  <si>
+    <t>Undefined</t>
   </si>
 </sst>
 </file>
@@ -6918,6 +6943,74 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A251961A-4424-404F-8F77-6EB707D782F5}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C2">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C3">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C4">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C5">
+        <v>20241213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F26964-D323-4807-93C3-4339F47CA786}">
   <dimension ref="A1:C11"/>

--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpoongundranar\Documents\Urban\NCCS\nccs-data-bmf\data\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC1D010-B9D6-4E7E-9E65-567729AE50E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB78C66-5609-405B-892C-5CB54F8DD50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="11" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
+    <workbookView xWindow="57480" yWindow="1290" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="6" xr2:uid="{1B4F8980-FB82-4AA6-95DF-3A9E10ACA6D4}"/>
   </bookViews>
   <sheets>
     <sheet name="status_code" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,15 @@
     <sheet name="income_code" sheetId="3" r:id="rId4"/>
     <sheet name="pf_filing_requirement_code" sheetId="5" r:id="rId5"/>
     <sheet name="ntee_code" sheetId="6" r:id="rId6"/>
-    <sheet name="ntee_code_activity_type" sheetId="7" r:id="rId7"/>
+    <sheet name="ntee_common_code" sheetId="7" r:id="rId7"/>
     <sheet name="ntee_code_major_group" sheetId="8" r:id="rId8"/>
     <sheet name="parent_organization" sheetId="9" r:id="rId9"/>
     <sheet name="subsection_classification_code" sheetId="10" r:id="rId10"/>
     <sheet name="affiliation_code" sheetId="11" r:id="rId11"/>
-    <sheet name="deductibility_code" sheetId="12" r:id="rId12"/>
+    <sheet name="foundation_code" sheetId="13" r:id="rId12"/>
+    <sheet name="organization_code" sheetId="14" r:id="rId13"/>
+    <sheet name="activity_code" sheetId="15" r:id="rId14"/>
+    <sheet name="deductibility_code" sheetId="12" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="2105">
   <si>
     <t>status_code</t>
   </si>
@@ -3596,12 +3599,6 @@
   </si>
   <si>
     <t>Religion-Related</t>
-  </si>
-  <si>
-    <t>ntee_activity_code</t>
-  </si>
-  <si>
-    <t>ntee_activity_code_definition</t>
   </si>
   <si>
     <t>effective_date</t>
@@ -5096,6 +5093,1284 @@
   </si>
   <si>
     <t>Undefined</t>
+  </si>
+  <si>
+    <t>foundation_code</t>
+  </si>
+  <si>
+    <t>foundation_code_definition</t>
+  </si>
+  <si>
+    <t>foundation_code_effective_date</t>
+  </si>
+  <si>
+    <t>Private operating foundation exempt from payment of section 4940 taxes on investment income</t>
+  </si>
+  <si>
+    <t>Private operating foundation</t>
+  </si>
+  <si>
+    <t>Private non-operating foundation</t>
+  </si>
+  <si>
+    <t>Suspense (a specific type not identified)</t>
+  </si>
+  <si>
+    <t>Church—IRC Section 170(b)(1)(A)(i)</t>
+  </si>
+  <si>
+    <t>School—IRC Section 170(b)(1)(A)(ii)</t>
+  </si>
+  <si>
+    <t>Hospital—IRC Section 170(b)(1)(A)(iii)</t>
+  </si>
+  <si>
+    <t>Organizations operated for the benefit of a college or university—IRC Section 170(b)(1)(A)(iv)</t>
+  </si>
+  <si>
+    <t>Federal, State or local government unit—IRC Section 170(b)(1)(A)(v)</t>
+  </si>
+  <si>
+    <t>Organization receiving support from governmental unit or general public—IRC Section 170(b)(1)(A)(vi)</t>
+  </si>
+  <si>
+    <t>General, public charity—IRC Section 509(a)(2)</t>
+  </si>
+  <si>
+    <t>Public charity supporting (FC 09–15)—IRC Section 509(a)(3)</t>
+  </si>
+  <si>
+    <t>Public safety—IRC Section 509(a)(4)</t>
+  </si>
+  <si>
+    <t>Supporting organization - IRC 509(a)(3) - Type I</t>
+  </si>
+  <si>
+    <t>Supporting organization - IRC 509(a)(3) - Type II</t>
+  </si>
+  <si>
+    <t>Supporting organization - IRC 509(a)(3) - Type III functionally integrated</t>
+  </si>
+  <si>
+    <t>Supporting organization - IRC 509(a)(3) - Type III not functionally integrated</t>
+  </si>
+  <si>
+    <t>organization_code</t>
+  </si>
+  <si>
+    <t>organization_code_definition</t>
+  </si>
+  <si>
+    <t>organization_code_effective_date</t>
+  </si>
+  <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
+    <t>Corporation</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Co-operative</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>Association</t>
+  </si>
+  <si>
+    <t>Non-exempt Charitable Trust</t>
+  </si>
+  <si>
+    <t>activity_code_category</t>
+  </si>
+  <si>
+    <t>activity_code</t>
+  </si>
+  <si>
+    <t>activity_code_definition</t>
+  </si>
+  <si>
+    <t>activity_code_notes</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Religious Activities</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Church, synagogue, etc.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Association or convention of churches</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Religious order</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Church auxiliary</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Mission</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Missionary activities</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>Evangelism</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Religious publishing activities</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Other religious activities</t>
+  </si>
+  <si>
+    <t>Book store</t>
+  </si>
+  <si>
+    <t>Use code 918</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>Genealogical activities</t>
+  </si>
+  <si>
+    <t>Use code 094</t>
+  </si>
+  <si>
+    <t>Schools Colleges And Related Activities</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>School, college, trade school, etc.</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>Special school for the blind, handicapped, etc.</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>Nursery school</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>Faculty group</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Alumni association or group</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>Parent or parent-teachers association</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>Key club</t>
+  </si>
+  <si>
+    <t>Use code 323 (Youth Organization)</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Other student society or group</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>School or college athletic association</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Scholarships for children of employees</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Scholarships (other)</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>Student loans</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>Student housing activities</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Other student aid</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>Student exchange with foreign country</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>Student operated business</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>Private school</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Other school related activities</t>
+  </si>
+  <si>
+    <t>Day care center</t>
+  </si>
+  <si>
+    <t>Use code 574</t>
+  </si>
+  <si>
+    <t>Financial support of schools, colleges, etc.</t>
+  </si>
+  <si>
+    <t>Use code 602</t>
+  </si>
+  <si>
+    <t>Achievement prizes or awards</t>
+  </si>
+  <si>
+    <t>Use code 914</t>
+  </si>
+  <si>
+    <t>Student bookstore</t>
+  </si>
+  <si>
+    <t>Student travel</t>
+  </si>
+  <si>
+    <t>Use code 299</t>
+  </si>
+  <si>
+    <t>See Notes</t>
+  </si>
+  <si>
+    <t>Scientific research</t>
+  </si>
+  <si>
+    <t>See Scientific Research Activities (180-199)</t>
+  </si>
+  <si>
+    <t>Cultural Historical Or Other Educational Activities</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Museum, zoo, planetarium, etc.</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>Historical site records or reenactment</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>Monument</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>Commemorative event (centennial, festival, pageant, etc.)</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>Fair</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>Community theatrical group</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Singing society or group</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Cultural performances</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Art exhibit</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Literary activities</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Cultural exchanges with foreign country</t>
+  </si>
+  <si>
+    <t>Other cultural or historical activities</t>
+  </si>
+  <si>
+    <t>Achievement prizes awards</t>
+  </si>
+  <si>
+    <t>Gifts or grants to individuals</t>
+  </si>
+  <si>
+    <t>Use code 561</t>
+  </si>
+  <si>
+    <t>Financial support of cultural organizations</t>
+  </si>
+  <si>
+    <t>Other Instructions And Training Activities</t>
+  </si>
+  <si>
+    <t>Publishing activities</t>
+  </si>
+  <si>
+    <t>Radio or television broadcasting</t>
+  </si>
+  <si>
+    <t>Producing films</t>
+  </si>
+  <si>
+    <t>Discussion groups, forums, panels lectures, etc.</t>
+  </si>
+  <si>
+    <t>Study and research (non-scientific)</t>
+  </si>
+  <si>
+    <t>Giving information or opinion</t>
+  </si>
+  <si>
+    <t>See also Advocacy (510-559)</t>
+  </si>
+  <si>
+    <t>Apprentice training</t>
+  </si>
+  <si>
+    <t>Other instruction and training</t>
+  </si>
+  <si>
+    <t>Travel tours</t>
+  </si>
+  <si>
+    <t>Health Services And Related Activities</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Hospital auxiliary</t>
+  </si>
+  <si>
+    <t>Nursing or convalescent home</t>
+  </si>
+  <si>
+    <t>Care and housing for the aged</t>
+  </si>
+  <si>
+    <t>See also 382</t>
+  </si>
+  <si>
+    <t>Rural medical facility</t>
+  </si>
+  <si>
+    <t>Blood bank</t>
+  </si>
+  <si>
+    <t>Rescue and emergency service</t>
+  </si>
+  <si>
+    <t>Nurses register or bureau</t>
+  </si>
+  <si>
+    <t>Aid to the handicapped</t>
+  </si>
+  <si>
+    <t>See also 031</t>
+  </si>
+  <si>
+    <t>Scientific research (diseases)</t>
+  </si>
+  <si>
+    <t>Other medical research</t>
+  </si>
+  <si>
+    <t>Health insurance (medical, dental, optical, etc.)</t>
+  </si>
+  <si>
+    <t>Prepared group health plan</t>
+  </si>
+  <si>
+    <t>Community health planning</t>
+  </si>
+  <si>
+    <t>Mental health care</t>
+  </si>
+  <si>
+    <t>Group medical practice association</t>
+  </si>
+  <si>
+    <t>In-faculty group practice association</t>
+  </si>
+  <si>
+    <t>Hospital pharmacy, parking facility, food services, etc.</t>
+  </si>
+  <si>
+    <t>Other health services</t>
+  </si>
+  <si>
+    <t>Scientific Research Activities</t>
+  </si>
+  <si>
+    <t>Contact or sponsored scientific research for industry</t>
+  </si>
+  <si>
+    <t>Scientific research for government</t>
+  </si>
+  <si>
+    <t>Other scientific research activities</t>
+  </si>
+  <si>
+    <t>Use code 161</t>
+  </si>
+  <si>
+    <t>Business And Professional Organizations</t>
+  </si>
+  <si>
+    <t>Business promotion (chamber of commerce, business league, etc.)</t>
+  </si>
+  <si>
+    <t>Real estate association</t>
+  </si>
+  <si>
+    <t>Board of trade</t>
+  </si>
+  <si>
+    <t>Regulating business</t>
+  </si>
+  <si>
+    <t>Promotion of fair business practices</t>
+  </si>
+  <si>
+    <t>Professional association</t>
+  </si>
+  <si>
+    <t>Professional association auxiliary</t>
+  </si>
+  <si>
+    <t>Industry trade shows</t>
+  </si>
+  <si>
+    <t>Convention displays</t>
+  </si>
+  <si>
+    <t>Research development and testing</t>
+  </si>
+  <si>
+    <t>Professional athletic league</t>
+  </si>
+  <si>
+    <t>Underwriting municipal insurance</t>
+  </si>
+  <si>
+    <t>Assigned risk insurance activities</t>
+  </si>
+  <si>
+    <t>Tourist bureau</t>
+  </si>
+  <si>
+    <t>Other business or professional group</t>
+  </si>
+  <si>
+    <t>Testing products of public safety</t>
+  </si>
+  <si>
+    <t>Use code 905</t>
+  </si>
+  <si>
+    <t>Attracting new industry</t>
+  </si>
+  <si>
+    <t>Use code 403</t>
+  </si>
+  <si>
+    <t>Use code 120</t>
+  </si>
+  <si>
+    <t>Insurance or other benefits for members</t>
+  </si>
+  <si>
+    <t>See Employee or Membership Benefit Organizations (260-279)</t>
+  </si>
+  <si>
+    <t>Farming And Related Activities</t>
+  </si>
+  <si>
+    <t>Farming</t>
+  </si>
+  <si>
+    <t>Farm bureau</t>
+  </si>
+  <si>
+    <t>Agricultural group</t>
+  </si>
+  <si>
+    <t>Horticultural group</t>
+  </si>
+  <si>
+    <t>Farmers cooperative marketing or purchasing</t>
+  </si>
+  <si>
+    <t>Farmers cooperative marketing or purchasing (Repeat in source)</t>
+  </si>
+  <si>
+    <t>Breeders association</t>
+  </si>
+  <si>
+    <t>Other farming and related activities</t>
+  </si>
+  <si>
+    <t>FFA, FHA, 4-H club, etc</t>
+  </si>
+  <si>
+    <t>Use code 322</t>
+  </si>
+  <si>
+    <t>Use code 065</t>
+  </si>
+  <si>
+    <t>Mutual Organizations</t>
+  </si>
+  <si>
+    <t>Mutual ditch, irrigation, telephone, electric company or like organization</t>
+  </si>
+  <si>
+    <t>Credit union</t>
+  </si>
+  <si>
+    <t>Reserve funds or insurance for domestic building and loan association, cooperative bank, or mutual savings bank</t>
+  </si>
+  <si>
+    <t>Mutual insurance company</t>
+  </si>
+  <si>
+    <t>Corporation organized under an Act of Congress</t>
+  </si>
+  <si>
+    <t>See also 904</t>
+  </si>
+  <si>
+    <t>Other mutual organization</t>
+  </si>
+  <si>
+    <t>Use code 234</t>
+  </si>
+  <si>
+    <t>Use code 157</t>
+  </si>
+  <si>
+    <t>Employee Or Membership Benefit Organizations</t>
+  </si>
+  <si>
+    <t>Fraternal Beneficiary society, order, or association</t>
+  </si>
+  <si>
+    <t>Improvement of conditions of workers</t>
+  </si>
+  <si>
+    <t>Association of municipal employees</t>
+  </si>
+  <si>
+    <t>Association of employees</t>
+  </si>
+  <si>
+    <t>Employee or member welfare association</t>
+  </si>
+  <si>
+    <t>Sick, accident, death, or similar benefits</t>
+  </si>
+  <si>
+    <t>Strike benefits</t>
+  </si>
+  <si>
+    <t>Unemployment benefits</t>
+  </si>
+  <si>
+    <t>Pension or retirement benefits</t>
+  </si>
+  <si>
+    <t>Vacation benefits</t>
+  </si>
+  <si>
+    <t>Other services or benefits to members or employees</t>
+  </si>
+  <si>
+    <t>Sports Athletic Recreational And Social Activities</t>
+  </si>
+  <si>
+    <t>Country club</t>
+  </si>
+  <si>
+    <t>Hobby club</t>
+  </si>
+  <si>
+    <t>Dinner club</t>
+  </si>
+  <si>
+    <t>Variety club</t>
+  </si>
+  <si>
+    <t>Dog club</t>
+  </si>
+  <si>
+    <t>Women's club</t>
+  </si>
+  <si>
+    <t>Hunting or fishing club</t>
+  </si>
+  <si>
+    <t>Swimming or tennis club</t>
+  </si>
+  <si>
+    <t>Other sports club</t>
+  </si>
+  <si>
+    <t>Community center</t>
+  </si>
+  <si>
+    <t>Community recreational facilities (park, playground, etc)</t>
+  </si>
+  <si>
+    <t>Training in sports</t>
+  </si>
+  <si>
+    <t>Amateur athletic association</t>
+  </si>
+  <si>
+    <t>Fundraising athletic or sports event</t>
+  </si>
+  <si>
+    <t>Other sports or athletic activities</t>
+  </si>
+  <si>
+    <t>Other recreational activities</t>
+  </si>
+  <si>
+    <t>Other social activities</t>
+  </si>
+  <si>
+    <t>Garden club</t>
+  </si>
+  <si>
+    <t>Use code 356</t>
+  </si>
+  <si>
+    <t>Boys Club, Little League, etc</t>
+  </si>
+  <si>
+    <t>Use code 321</t>
+  </si>
+  <si>
+    <t>Use code 038</t>
+  </si>
+  <si>
+    <t>Youth Activities</t>
+  </si>
+  <si>
+    <t>Boy Scouts, Girl Scouts, etc.</t>
+  </si>
+  <si>
+    <t>Boys Club, Little League, etc.</t>
+  </si>
+  <si>
+    <t>FFA, FHA, 4-H club, etc.</t>
+  </si>
+  <si>
+    <t>YMCA, YWCA, etc.</t>
+  </si>
+  <si>
+    <t>Camp</t>
+  </si>
+  <si>
+    <t>Care and housing of children (orphanage, etc)</t>
+  </si>
+  <si>
+    <t>Prevention of cruelty to children</t>
+  </si>
+  <si>
+    <t>Combat juvenile delinquency</t>
+  </si>
+  <si>
+    <t>Other youth organization or activities</t>
+  </si>
+  <si>
+    <t>Conservation Environmental And Beautification Activities</t>
+  </si>
+  <si>
+    <t>Preservation of natural resources (conservation)</t>
+  </si>
+  <si>
+    <t>Combating or preventing pollution (air, water, etc)</t>
+  </si>
+  <si>
+    <t>Land acquisition for preservation</t>
+  </si>
+  <si>
+    <t>Soil or water conservation</t>
+  </si>
+  <si>
+    <t>Preservation of scenic beauty</t>
+  </si>
+  <si>
+    <t>Wildlife sanctuary or refuge</t>
+  </si>
+  <si>
+    <t>Other conservation environmental or beautification activities</t>
+  </si>
+  <si>
+    <t>Litigation</t>
+  </si>
+  <si>
+    <t>See Litigation and Legal Aid Activities (460-465)</t>
+  </si>
+  <si>
+    <t>Combat community deterioration</t>
+  </si>
+  <si>
+    <t>Use code 402</t>
+  </si>
+  <si>
+    <t>Housing Activities</t>
+  </si>
+  <si>
+    <t>Low-income housing</t>
+  </si>
+  <si>
+    <t>Low and moderate income housing</t>
+  </si>
+  <si>
+    <t>Housing for the aged</t>
+  </si>
+  <si>
+    <t>See also 153</t>
+  </si>
+  <si>
+    <t>Instruction and guidance on housing</t>
+  </si>
+  <si>
+    <t>Other housing activities</t>
+  </si>
+  <si>
+    <t>Use code 152</t>
+  </si>
+  <si>
+    <t>Student housing</t>
+  </si>
+  <si>
+    <t>Use code 042</t>
+  </si>
+  <si>
+    <t>Orphanage</t>
+  </si>
+  <si>
+    <t>Use code 326</t>
+  </si>
+  <si>
+    <t>Inner City Or Community Activities</t>
+  </si>
+  <si>
+    <t>Area development redevelopment of renewal</t>
+  </si>
+  <si>
+    <t>Homeowners' association</t>
+  </si>
+  <si>
+    <t>Other activity aimed to combating community deterioration</t>
+  </si>
+  <si>
+    <t>Attracting new industry or retaining industry in an area</t>
+  </si>
+  <si>
+    <t>Community promotion</t>
+  </si>
+  <si>
+    <t>Loans or grants for minority businesses</t>
+  </si>
+  <si>
+    <t>Crime prevention</t>
+  </si>
+  <si>
+    <t>Voluntary firemen's organization or auxiliary</t>
+  </si>
+  <si>
+    <t>Community service organization</t>
+  </si>
+  <si>
+    <t>Other inner city or community benefit activities</t>
+  </si>
+  <si>
+    <t>Community recreational facility</t>
+  </si>
+  <si>
+    <t>Use code 297</t>
+  </si>
+  <si>
+    <t>Use code 296</t>
+  </si>
+  <si>
+    <t>Job training, counseling, or assistance</t>
+  </si>
+  <si>
+    <t>Use code 566</t>
+  </si>
+  <si>
+    <t>Referral service (social agencies)</t>
+  </si>
+  <si>
+    <t>Use code 569</t>
+  </si>
+  <si>
+    <t>Legal aid to indigents</t>
+  </si>
+  <si>
+    <t>Use code 462</t>
+  </si>
+  <si>
+    <t>Rescue squad</t>
+  </si>
+  <si>
+    <t>Use code 158</t>
+  </si>
+  <si>
+    <t>Civil Rights Activities</t>
+  </si>
+  <si>
+    <t>Defense of human and civil rights</t>
+  </si>
+  <si>
+    <t>Elimination of prejudice and discrimination (race, religion, sex, national origin, etc)</t>
+  </si>
+  <si>
+    <t>Lessen neighborhood tensions</t>
+  </si>
+  <si>
+    <t>Other civil rights activities</t>
+  </si>
+  <si>
+    <t>Litigation And Legal Aid Activities</t>
+  </si>
+  <si>
+    <t>Public interest litigation activities</t>
+  </si>
+  <si>
+    <t>Other litigation or support of litigation</t>
+  </si>
+  <si>
+    <t>Providing bail</t>
+  </si>
+  <si>
+    <t>Plan under IRC section 120</t>
+  </si>
+  <si>
+    <t>Legislative And Political Activities</t>
+  </si>
+  <si>
+    <t>Propose, support, or oppose legislation</t>
+  </si>
+  <si>
+    <t>Voter information on issues or candidates</t>
+  </si>
+  <si>
+    <t>Voter education (mechanics of registering, voting etc.)</t>
+  </si>
+  <si>
+    <t>Support, oppose, or rate political candidates</t>
+  </si>
+  <si>
+    <t>Provide facilities or services for political campaign activities</t>
+  </si>
+  <si>
+    <t>Other legislative and political activities</t>
+  </si>
+  <si>
+    <t>Advocacy</t>
+  </si>
+  <si>
+    <t>Firearms control</t>
+  </si>
+  <si>
+    <t>Selective Service System</t>
+  </si>
+  <si>
+    <t>National defense policy</t>
+  </si>
+  <si>
+    <t>Weapons systems</t>
+  </si>
+  <si>
+    <t>Government spending</t>
+  </si>
+  <si>
+    <t>Taxes or tax exemption</t>
+  </si>
+  <si>
+    <t>Separation of church and state</t>
+  </si>
+  <si>
+    <t>Government aid to parochial schools</t>
+  </si>
+  <si>
+    <t>U.S. foreign policy</t>
+  </si>
+  <si>
+    <t>U.S. military involvement</t>
+  </si>
+  <si>
+    <t>Pacifism and peace</t>
+  </si>
+  <si>
+    <t>Economic-political system of U.S.</t>
+  </si>
+  <si>
+    <t>Anti-communism</t>
+  </si>
+  <si>
+    <t>Right to work</t>
+  </si>
+  <si>
+    <t>Zoning or rezoning</t>
+  </si>
+  <si>
+    <t>Location of highway or transportation system</t>
+  </si>
+  <si>
+    <t>Rights of criminal defendants</t>
+  </si>
+  <si>
+    <t>Capital punishment</t>
+  </si>
+  <si>
+    <t>Stricter law enforcement</t>
+  </si>
+  <si>
+    <t>Ecology or conservation</t>
+  </si>
+  <si>
+    <t>Protection of consumer interests</t>
+  </si>
+  <si>
+    <t>Medical care service</t>
+  </si>
+  <si>
+    <t>Welfare systems</t>
+  </si>
+  <si>
+    <t>Urban renewal</t>
+  </si>
+  <si>
+    <t>Busing student to achieve racial balance</t>
+  </si>
+  <si>
+    <t>Racial integration</t>
+  </si>
+  <si>
+    <t>Use of intoxicating beverage</t>
+  </si>
+  <si>
+    <t>Use of drugs or narcotics</t>
+  </si>
+  <si>
+    <t>Use of tobacco</t>
+  </si>
+  <si>
+    <t>Prohibition of erotica</t>
+  </si>
+  <si>
+    <t>Sex education in public schools</t>
+  </si>
+  <si>
+    <t>Population control</t>
+  </si>
+  <si>
+    <t>Birth control methods</t>
+  </si>
+  <si>
+    <t>Legalized abortion</t>
+  </si>
+  <si>
+    <t>Other matters</t>
+  </si>
+  <si>
+    <t>Other Social And Welfare Activities</t>
+  </si>
+  <si>
+    <t>Supplying money goods or services to the poor</t>
+  </si>
+  <si>
+    <t>Gifts or grants to individuals (other than scholarships)</t>
+  </si>
+  <si>
+    <t>Other loans to individuals</t>
+  </si>
+  <si>
+    <t>Marriage counseling</t>
+  </si>
+  <si>
+    <t>Family planning</t>
+  </si>
+  <si>
+    <t>Credit counseling and assistance</t>
+  </si>
+  <si>
+    <t>Draft counseling</t>
+  </si>
+  <si>
+    <t>Vocational counseling</t>
+  </si>
+  <si>
+    <t>Rehabilitating convicts or ex-convicts</t>
+  </si>
+  <si>
+    <t>Rehabilitating alcoholics, drug abusers, compulsive gamblers, etc.</t>
+  </si>
+  <si>
+    <t>Services for the aged</t>
+  </si>
+  <si>
+    <t>See also 153 and 382</t>
+  </si>
+  <si>
+    <t>Use code 039</t>
+  </si>
+  <si>
+    <t>Use code 040</t>
+  </si>
+  <si>
+    <t>Use code 041</t>
+  </si>
+  <si>
+    <t>Training or aid to the handicapped</t>
+  </si>
+  <si>
+    <t>See 031 and 160</t>
+  </si>
+  <si>
+    <t>Activities And Purposes</t>
+  </si>
+  <si>
+    <t>Community Chest, United Way, etc.</t>
+  </si>
+  <si>
+    <t>Booster club</t>
+  </si>
+  <si>
+    <t>Gifts grants or loans to other organizations</t>
+  </si>
+  <si>
+    <t>Non-financial services of facilities to other organizations</t>
+  </si>
+  <si>
+    <t>Other Purposes And Activities</t>
+  </si>
+  <si>
+    <t>Cemetery or burial activities</t>
+  </si>
+  <si>
+    <t>Perpetual (care fund (cemetery, columbarium, etc)</t>
+  </si>
+  <si>
+    <t>Emergency or disaster aid fund</t>
+  </si>
+  <si>
+    <t>Community trust or component</t>
+  </si>
+  <si>
+    <t>Government instrumentality or agency</t>
+  </si>
+  <si>
+    <t>See also 254</t>
+  </si>
+  <si>
+    <t>Testing products for public safety</t>
+  </si>
+  <si>
+    <t>Consumer interest group</t>
+  </si>
+  <si>
+    <t>Veterans activities</t>
+  </si>
+  <si>
+    <t>Patriotic activities</t>
+  </si>
+  <si>
+    <t>Non-exempt charitable trust described in section 4947(a)(1) of the Code</t>
+  </si>
+  <si>
+    <t>Domestic organization with activities outside U.S.</t>
+  </si>
+  <si>
+    <t>Foreign organization</t>
+  </si>
+  <si>
+    <t>Title holding corporation</t>
+  </si>
+  <si>
+    <t>Prevention of cruelty to animals</t>
+  </si>
+  <si>
+    <t>Achievement pries of awards</t>
+  </si>
+  <si>
+    <t>Erection or maintenance of public building or works</t>
+  </si>
+  <si>
+    <t>Cafeteria, restaurant, snack bar, food services, etc.</t>
+  </si>
+  <si>
+    <t>Thrift ship, retail outlet, etc.</t>
+  </si>
+  <si>
+    <t>Book, gift or supply store</t>
+  </si>
+  <si>
+    <t>Advertising</t>
+  </si>
+  <si>
+    <t>Loans or credit reporting</t>
+  </si>
+  <si>
+    <t>Endowment fund or financial services</t>
+  </si>
+  <si>
+    <t>Indians (tribes, cultures, etc.)</t>
+  </si>
+  <si>
+    <t>Traffic or tariff bureau</t>
+  </si>
+  <si>
+    <t>Section 501(c)(1) with 50% deductibility</t>
+  </si>
+  <si>
+    <t>Government instrumentality other than section 501(c)</t>
+  </si>
+  <si>
+    <t>4947(a)(2) trust</t>
+  </si>
+  <si>
+    <t>Prepaid legal services pan exempt under IRC section 501(c)(20)</t>
+  </si>
+  <si>
+    <t>Withdrawal liability payment fund</t>
+  </si>
+  <si>
+    <t>Section 501(k) child care organization</t>
+  </si>
+  <si>
+    <t>Described in section 170(b)1)(a)(vi) of the Code</t>
+  </si>
+  <si>
+    <t>Described in section 509(a)(2) of the Code</t>
+  </si>
+  <si>
+    <t>Unspecified</t>
+  </si>
+  <si>
+    <t>ntee_common_code</t>
+  </si>
+  <si>
+    <t>ntee_common_code_definition</t>
   </si>
 </sst>
 </file>
@@ -5194,7 +6469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5213,6 +6488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5602,22 +6878,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C1" t="s">
         <v>1552</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1553</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1554</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>1555</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1557</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5628,10 +6904,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="D2" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="E2">
         <v>20241213</v>
@@ -5648,10 +6924,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D3" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="E3">
         <v>20241213</v>
@@ -5668,10 +6944,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="D4" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E4">
         <v>20241213</v>
@@ -5688,10 +6964,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D5" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E5">
         <v>20241213</v>
@@ -5708,10 +6984,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D6" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E6">
         <v>20241213</v>
@@ -5728,10 +7004,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D7" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E7">
         <v>20241213</v>
@@ -5748,10 +7024,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D8" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E8">
         <v>20241213</v>
@@ -5768,10 +7044,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D9" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E9">
         <v>20241213</v>
@@ -5788,10 +7064,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D10" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E10">
         <v>20241213</v>
@@ -5808,10 +7084,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D11" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E11">
         <v>20241213</v>
@@ -5828,10 +7104,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="D12" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="E12">
         <v>20241213</v>
@@ -5848,10 +7124,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="D13" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="E13">
         <v>20241213</v>
@@ -5868,10 +7144,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="D14" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="E14">
         <v>20241213</v>
@@ -5888,10 +7164,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="D15" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E15">
         <v>20241213</v>
@@ -5908,10 +7184,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="D16" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E16">
         <v>20241213</v>
@@ -5928,10 +7204,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="D17" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E17">
         <v>20241213</v>
@@ -5948,10 +7224,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D18" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E18">
         <v>20241213</v>
@@ -5968,10 +7244,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D19" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E19">
         <v>20241213</v>
@@ -5988,10 +7264,10 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D20" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E20">
         <v>20241213</v>
@@ -6008,10 +7284,10 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D21" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E21">
         <v>20241213</v>
@@ -6028,10 +7304,10 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="D22" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="E22">
         <v>20241213</v>
@@ -6048,10 +7324,10 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D23" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="E23">
         <v>20241213</v>
@@ -6068,10 +7344,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="D24" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="E24">
         <v>20241213</v>
@@ -6088,10 +7364,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="D25" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="E25">
         <v>20241213</v>
@@ -6108,10 +7384,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D26" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="E26">
         <v>20241213</v>
@@ -6128,10 +7404,10 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D27" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="E27">
         <v>20241213</v>
@@ -6148,10 +7424,10 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D28" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E28">
         <v>20241213</v>
@@ -6168,10 +7444,10 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="D29" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E29">
         <v>20241213</v>
@@ -6188,10 +7464,10 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="D30" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E30">
         <v>20241213</v>
@@ -6208,10 +7484,10 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D31" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E31">
         <v>20241213</v>
@@ -6228,10 +7504,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="D32" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E32">
         <v>20241213</v>
@@ -6248,10 +7524,10 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D33" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E33">
         <v>20241213</v>
@@ -6268,10 +7544,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="D34" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="E34">
         <v>20241213</v>
@@ -6288,10 +7564,10 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D35" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="E35">
         <v>20241213</v>
@@ -6308,10 +7584,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="D36" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="E36">
         <v>20241213</v>
@@ -6328,10 +7604,10 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="D37" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="E37">
         <v>20241213</v>
@@ -6348,10 +7624,10 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D38" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="E38">
         <v>20241213</v>
@@ -6368,10 +7644,10 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="D39" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="E39">
         <v>20241213</v>
@@ -6388,10 +7664,10 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D40" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="E40">
         <v>20241213</v>
@@ -6408,10 +7684,10 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="D41" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="E41">
         <v>20241213</v>
@@ -6428,10 +7704,10 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="D42" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="E42">
         <v>20241213</v>
@@ -6448,10 +7724,10 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="E43">
         <v>20241213</v>
@@ -6468,10 +7744,10 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D44" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="E44">
         <v>20241213</v>
@@ -6488,10 +7764,10 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D45" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="E45">
         <v>20241213</v>
@@ -6508,10 +7784,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D46" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="E46">
         <v>20241213</v>
@@ -6528,10 +7804,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D47" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="E47">
         <v>20241213</v>
@@ -6548,10 +7824,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D48" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E48">
         <v>20241213</v>
@@ -6568,10 +7844,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D49" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="E49">
         <v>20241213</v>
@@ -6588,10 +7864,10 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D50" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="E50">
         <v>20241213</v>
@@ -6608,10 +7884,10 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D51" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="E51">
         <v>20241213</v>
@@ -6628,10 +7904,10 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="D52" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="E52">
         <v>20241213</v>
@@ -6648,10 +7924,10 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="D53" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E53">
         <v>20241213</v>
@@ -6668,10 +7944,10 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="D54" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="E54">
         <v>20241213</v>
@@ -6688,10 +7964,10 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="D55" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E55">
         <v>20241213</v>
@@ -6708,7 +7984,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="D56">
         <v>521</v>
@@ -6728,7 +8004,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="D57">
         <v>529</v>
@@ -6748,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="D58">
         <v>82</v>
@@ -6768,10 +8044,10 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="D59" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="E59">
         <v>20241213</v>
@@ -6788,10 +8064,10 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="D60" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="E60">
         <v>20241213</v>
@@ -6808,10 +8084,10 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="D61" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="E61">
         <v>20241213</v>
@@ -6828,10 +8104,10 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D62" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="E62">
         <v>20241213</v>
@@ -6847,95 +8123,106 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B295775B-C545-42EF-B1E6-C8444CDB5163}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C1" t="s">
         <v>1656</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1659</v>
+        <v>1678</v>
       </c>
       <c r="C2" t="s">
-        <v>1660</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="C3" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
       <c r="C4" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="C5" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="C6" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="C7" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>1671</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1672</v>
+      <c r="B9" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1670</v>
       </c>
     </row>
   </sheetData>
@@ -6944,22 +8231,3862 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73B4971-00A1-40E6-B8DA-3C9D5FED13D3}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C2">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C3">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C4">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C5">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C6">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C7">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C8">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C9">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C10">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C11">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C12">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C13">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C14">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C15">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C16">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C17">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C18">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C19">
+        <v>20241213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C4753D-37E7-4F27-8944-5A62AA738474}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C2">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C3">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C4">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C5">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C6">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C7">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C8">
+        <v>20241213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF794D5B-8B9D-4606-973E-547C5F04456C}">
+  <dimension ref="A1:D306"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B12">
+        <v>918</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B32">
+        <v>574</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B33">
+        <v>602</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B34">
+        <v>914</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B35">
+        <v>918</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B36">
+        <v>299</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B51">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B52">
+        <v>914</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B53">
+        <v>561</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B54">
+        <v>602</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B55">
+        <v>120</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B56">
+        <v>121</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B57">
+        <v>122</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B58">
+        <v>123</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B59">
+        <v>124</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B60">
+        <v>125</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B61">
+        <v>126</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B62">
+        <v>149</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B63">
+        <v>299</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B64">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B65">
+        <v>151</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B66">
+        <v>152</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B67">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B68">
+        <v>155</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B69">
+        <v>156</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B70">
+        <v>157</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B71">
+        <v>158</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B72">
+        <v>159</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B73">
+        <v>160</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B74">
+        <v>161</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B75">
+        <v>162</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B76">
+        <v>163</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B77">
+        <v>164</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B78">
+        <v>165</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B79">
+        <v>166</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B80">
+        <v>167</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B81">
+        <v>168</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B82">
+        <v>169</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B83">
+        <v>179</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B84">
+        <v>180</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B85">
+        <v>181</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B86">
+        <v>199</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B87">
+        <v>161</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B88">
+        <v>200</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B89">
+        <v>201</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B90">
+        <v>202</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B91">
+        <v>203</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B92">
+        <v>204</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B93">
+        <v>205</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B94">
+        <v>206</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B95">
+        <v>207</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B96">
+        <v>208</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B97">
+        <v>209</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B98">
+        <v>210</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B99">
+        <v>211</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B100">
+        <v>212</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B101">
+        <v>213</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B102">
+        <v>229</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B103">
+        <v>905</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B104">
+        <v>403</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B105">
+        <v>120</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B107">
+        <v>230</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B108">
+        <v>231</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B109">
+        <v>232</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B110">
+        <v>233</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B111">
+        <v>234</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B112">
+        <v>235</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B113">
+        <v>237</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B114">
+        <v>249</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B115">
+        <v>322</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B117">
+        <v>250</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B118">
+        <v>251</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B119">
+        <v>252</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B120">
+        <v>253</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B121">
+        <v>254</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B122">
+        <v>259</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B123">
+        <v>234</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B124">
+        <v>157</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B125">
+        <v>260</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B126">
+        <v>261</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B127">
+        <v>262</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B128">
+        <v>263</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B129">
+        <v>264</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B130">
+        <v>265</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B131">
+        <v>266</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B132">
+        <v>267</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B133">
+        <v>268</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B134">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B135">
+        <v>279</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B136">
+        <v>280</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B137">
+        <v>281</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B138">
+        <v>282</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B139">
+        <v>283</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B140">
+        <v>284</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B141">
+        <v>285</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B142">
+        <v>286</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B143">
+        <v>287</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B144">
+        <v>288</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B145">
+        <v>296</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B146">
+        <v>297</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B147">
+        <v>298</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B148">
+        <v>299</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B149">
+        <v>300</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B150">
+        <v>301</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B151">
+        <v>317</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B152">
+        <v>318</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B153">
+        <v>319</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B154">
+        <v>356</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B155">
+        <v>321</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B157">
+        <v>320</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B158">
+        <v>321</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B159">
+        <v>322</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B160">
+        <v>324</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B161">
+        <v>325</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B162">
+        <v>326</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B163">
+        <v>327</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B164">
+        <v>328</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B165">
+        <v>349</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B166">
+        <v>350</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B167">
+        <v>351</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B168">
+        <v>352</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B169">
+        <v>353</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B170">
+        <v>354</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B171">
+        <v>355</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B172">
+        <v>356</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B173">
+        <v>379</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B175">
+        <v>402</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B176">
+        <v>380</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B177">
+        <v>381</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B178">
+        <v>382</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B179">
+        <v>398</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B180">
+        <v>399</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B181">
+        <v>152</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B183">
+        <v>326</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B184">
+        <v>400</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B185">
+        <v>401</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B186">
+        <v>402</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B187">
+        <v>403</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B188">
+        <v>404</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B189">
+        <v>405</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B190">
+        <v>406</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B191">
+        <v>407</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B192">
+        <v>408</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B193">
+        <v>429</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B194">
+        <v>297</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B195">
+        <v>296</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B196">
+        <v>566</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B197">
+        <v>574</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B198">
+        <v>569</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B199">
+        <v>462</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B200">
+        <v>158</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B201">
+        <v>430</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B202">
+        <v>431</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B203">
+        <v>432</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B204">
+        <v>449</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B205">
+        <v>460</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B206">
+        <v>461</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B207">
+        <v>462</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B208">
+        <v>463</v>
+      </c>
+      <c r="C208" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B209">
+        <v>465</v>
+      </c>
+      <c r="C209" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B210">
+        <v>480</v>
+      </c>
+      <c r="C210" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B211">
+        <v>481</v>
+      </c>
+      <c r="C211" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B212">
+        <v>482</v>
+      </c>
+      <c r="C212" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B213">
+        <v>483</v>
+      </c>
+      <c r="C213" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B214">
+        <v>484</v>
+      </c>
+      <c r="C214" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B215">
+        <v>509</v>
+      </c>
+      <c r="C215" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B216">
+        <v>510</v>
+      </c>
+      <c r="C216" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B217">
+        <v>511</v>
+      </c>
+      <c r="C217" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B218">
+        <v>512</v>
+      </c>
+      <c r="C218" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B219">
+        <v>513</v>
+      </c>
+      <c r="C219" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B220">
+        <v>514</v>
+      </c>
+      <c r="C220" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B221">
+        <v>515</v>
+      </c>
+      <c r="C221" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B222">
+        <v>516</v>
+      </c>
+      <c r="C222" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B223">
+        <v>517</v>
+      </c>
+      <c r="C223" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B224">
+        <v>518</v>
+      </c>
+      <c r="C224" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B225">
+        <v>519</v>
+      </c>
+      <c r="C225" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B226">
+        <v>520</v>
+      </c>
+      <c r="C226" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B227">
+        <v>521</v>
+      </c>
+      <c r="C227" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B228">
+        <v>522</v>
+      </c>
+      <c r="C228" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B229">
+        <v>523</v>
+      </c>
+      <c r="C229" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B230">
+        <v>524</v>
+      </c>
+      <c r="C230" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B231">
+        <v>525</v>
+      </c>
+      <c r="C231" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B232">
+        <v>526</v>
+      </c>
+      <c r="C232" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B233">
+        <v>527</v>
+      </c>
+      <c r="C233" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B234">
+        <v>528</v>
+      </c>
+      <c r="C234" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B235">
+        <v>529</v>
+      </c>
+      <c r="C235" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B236">
+        <v>530</v>
+      </c>
+      <c r="C236" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B237">
+        <v>531</v>
+      </c>
+      <c r="C237" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B238">
+        <v>532</v>
+      </c>
+      <c r="C238" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B239">
+        <v>533</v>
+      </c>
+      <c r="C239" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B240">
+        <v>534</v>
+      </c>
+      <c r="C240" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B241">
+        <v>535</v>
+      </c>
+      <c r="C241" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B242">
+        <v>536</v>
+      </c>
+      <c r="C242" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B243">
+        <v>537</v>
+      </c>
+      <c r="C243" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B244">
+        <v>538</v>
+      </c>
+      <c r="C244" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B245">
+        <v>539</v>
+      </c>
+      <c r="C245" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B246">
+        <v>540</v>
+      </c>
+      <c r="C246" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B247">
+        <v>541</v>
+      </c>
+      <c r="C247" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B248">
+        <v>542</v>
+      </c>
+      <c r="C248" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B249">
+        <v>543</v>
+      </c>
+      <c r="C249" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B250">
+        <v>559</v>
+      </c>
+      <c r="C250" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B251">
+        <v>560</v>
+      </c>
+      <c r="C251" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B252">
+        <v>561</v>
+      </c>
+      <c r="C252" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B253">
+        <v>562</v>
+      </c>
+      <c r="C253" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B254">
+        <v>563</v>
+      </c>
+      <c r="C254" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B255">
+        <v>564</v>
+      </c>
+      <c r="C255" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B256">
+        <v>565</v>
+      </c>
+      <c r="C256" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B257">
+        <v>566</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B258">
+        <v>567</v>
+      </c>
+      <c r="C258" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B259">
+        <v>568</v>
+      </c>
+      <c r="C259" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B260">
+        <v>569</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B261">
+        <v>572</v>
+      </c>
+      <c r="C261" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B262">
+        <v>573</v>
+      </c>
+      <c r="C262" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B263">
+        <v>574</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B264">
+        <v>575</v>
+      </c>
+      <c r="C264" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D264" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D265" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D266" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D267" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C268" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D268" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B269">
+        <v>600</v>
+      </c>
+      <c r="C269" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B270">
+        <v>601</v>
+      </c>
+      <c r="C270" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B271">
+        <v>602</v>
+      </c>
+      <c r="C271" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B272">
+        <v>603</v>
+      </c>
+      <c r="C272" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B273">
+        <v>900</v>
+      </c>
+      <c r="C273" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B274">
+        <v>901</v>
+      </c>
+      <c r="C274" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B275">
+        <v>902</v>
+      </c>
+      <c r="C275" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B276">
+        <v>903</v>
+      </c>
+      <c r="C276" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B277">
+        <v>904</v>
+      </c>
+      <c r="C277" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D277" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B278">
+        <v>905</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B279">
+        <v>906</v>
+      </c>
+      <c r="C279" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B280">
+        <v>907</v>
+      </c>
+      <c r="C280" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B281">
+        <v>908</v>
+      </c>
+      <c r="C281" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B282">
+        <v>909</v>
+      </c>
+      <c r="C282" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B283">
+        <v>910</v>
+      </c>
+      <c r="C283" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B284">
+        <v>911</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B285">
+        <v>912</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B286">
+        <v>913</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B287">
+        <v>914</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B288">
+        <v>915</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B289">
+        <v>916</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B290">
+        <v>917</v>
+      </c>
+      <c r="C290" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B291">
+        <v>918</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B292">
+        <v>919</v>
+      </c>
+      <c r="C292" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B293">
+        <v>920</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B294">
+        <v>921</v>
+      </c>
+      <c r="C294" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B295">
+        <v>922</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B296">
+        <v>923</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B297">
+        <v>924</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B298">
+        <v>925</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B299">
+        <v>926</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B300">
+        <v>928</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B301">
+        <v>930</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B302">
+        <v>931</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B303">
+        <v>990</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B304">
+        <v>994</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B305">
+        <v>995</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B306">
+        <v>998</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A251961A-4424-404F-8F77-6EB707D782F5}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1" t="s">
         <v>1673</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1674</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1675</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1676</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6967,7 +12094,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C2">
         <v>20241213</v>
@@ -6978,7 +12105,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C3">
         <v>20241213</v>
@@ -6989,7 +12116,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C4">
         <v>20241213</v>
@@ -7000,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C5">
         <v>20241213</v>
@@ -7486,13 +12613,13 @@
         <v>121</v>
       </c>
       <c r="B1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C1" t="s">
         <v>1169</v>
       </c>
       <c r="D1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11532,7 +16659,7 @@
         <v>553</v>
       </c>
       <c r="B290" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C290" t="s">
         <v>554</v>
@@ -11546,7 +16673,7 @@
         <v>555</v>
       </c>
       <c r="B291" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C291" t="s">
         <v>556</v>
@@ -11560,7 +16687,7 @@
         <v>557</v>
       </c>
       <c r="B292" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C292" t="s">
         <v>558</v>
@@ -11574,7 +16701,7 @@
         <v>559</v>
       </c>
       <c r="B293" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C293" t="s">
         <v>560</v>
@@ -11588,7 +16715,7 @@
         <v>561</v>
       </c>
       <c r="B294" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C294" t="s">
         <v>562</v>
@@ -11602,7 +16729,7 @@
         <v>563</v>
       </c>
       <c r="B295" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C295" t="s">
         <v>564</v>
@@ -11616,7 +16743,7 @@
         <v>565</v>
       </c>
       <c r="B296" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C296" t="s">
         <v>566</v>
@@ -11630,7 +16757,7 @@
         <v>567</v>
       </c>
       <c r="B297" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C297" t="s">
         <v>568</v>
@@ -11644,7 +16771,7 @@
         <v>569</v>
       </c>
       <c r="B298" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C298" t="s">
         <v>570</v>
@@ -11658,7 +16785,7 @@
         <v>571</v>
       </c>
       <c r="B299" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C299" t="s">
         <v>572</v>
@@ -11672,7 +16799,7 @@
         <v>573</v>
       </c>
       <c r="B300" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C300" t="s">
         <v>574</v>
@@ -11686,7 +16813,7 @@
         <v>575</v>
       </c>
       <c r="B301" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C301" t="s">
         <v>576</v>
@@ -11700,7 +16827,7 @@
         <v>577</v>
       </c>
       <c r="B302" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C302" t="s">
         <v>578</v>
@@ -11714,7 +16841,7 @@
         <v>579</v>
       </c>
       <c r="B303" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C303" t="s">
         <v>580</v>
@@ -11728,7 +16855,7 @@
         <v>581</v>
       </c>
       <c r="B304" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C304" t="s">
         <v>582</v>
@@ -12344,7 +17471,7 @@
         <v>648</v>
       </c>
       <c r="B348" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C348" t="s">
         <v>649</v>
@@ -12358,7 +17485,7 @@
         <v>650</v>
       </c>
       <c r="B349" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C349" t="s">
         <v>651</v>
@@ -16488,7 +21615,7 @@
         <v>1163</v>
       </c>
       <c r="B644" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C644" t="s">
         <v>1164</v>
@@ -16505,7 +21632,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE500F7-831C-4EBB-9F2C-320470D3046D}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="2" bestFit="1" customWidth="1"/>
@@ -16515,18 +21642,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C1" t="s">
         <v>1183</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -16537,10 +21664,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B3" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C3">
         <v>19990101</v>
@@ -16548,10 +21675,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B4" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C4">
         <v>19990101</v>
@@ -16559,7 +21686,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -16570,10 +21697,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B6" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C6">
         <v>19990101</v>
@@ -16581,10 +21708,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B7" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C7">
         <v>19990101</v>
@@ -16592,13 +21719,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B8" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C8">
         <v>19990101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C9">
+        <v>20250101</v>
       </c>
     </row>
   </sheetData>
@@ -16616,18 +21754,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B2" t="s">
         <v>1170</v>
@@ -16638,7 +21776,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B3" t="s">
         <v>124</v>
@@ -16649,7 +21787,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B4" t="s">
         <v>1171</v>
@@ -16660,7 +21798,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B5" t="s">
         <v>1172</v>
@@ -16671,7 +21809,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B6" t="s">
         <v>1173</v>
@@ -16682,10 +21820,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B7" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C7">
         <v>20251115</v>
@@ -16693,10 +21831,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B8" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C8">
         <v>20251115</v>
@@ -16704,7 +21842,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B9" t="s">
         <v>1174</v>
@@ -16715,10 +21853,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B10" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C10">
         <v>20251115</v>
@@ -16726,7 +21864,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B11" t="s">
         <v>1175</v>
@@ -16737,7 +21875,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B12" t="s">
         <v>1176</v>
@@ -16748,10 +21886,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B13" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C13">
         <v>20251115</v>
@@ -16759,7 +21897,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B14" t="s">
         <v>1177</v>
@@ -16770,10 +21908,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B15" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C15">
         <v>20251115</v>
@@ -16781,7 +21919,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B16" t="s">
         <v>1178</v>
@@ -16792,7 +21930,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B17" t="s">
         <v>1179</v>
@@ -16803,7 +21941,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B18" t="s">
         <v>1180</v>
@@ -16814,10 +21952,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B19" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C19">
         <v>20251115</v>
@@ -16825,10 +21963,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B20" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C20">
         <v>20251115</v>
@@ -16836,7 +21974,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B21" t="s">
         <v>1181</v>
@@ -16847,10 +21985,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B22" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C22">
         <v>20251115</v>
@@ -16858,7 +21996,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B23" t="s">
         <v>1027</v>
@@ -16869,10 +22007,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B24" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C24">
         <v>20251115</v>
@@ -16880,7 +22018,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B25" t="s">
         <v>1182</v>
@@ -16891,10 +22029,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B26" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C26">
         <v>20251115</v>
@@ -16902,7 +22040,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B27" t="s">
         <v>1164</v>
@@ -16928,39 +22066,39 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1548</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C2" s="7"/>
     </row>
     <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C4" s="7">
         <v>526</v>
@@ -16968,10 +22106,10 @@
     </row>
     <row r="5" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C5" s="7">
         <v>948</v>
@@ -16979,10 +22117,10 @@
     </row>
     <row r="6" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C6" s="7">
         <v>1403</v>
@@ -16990,10 +22128,10 @@
     </row>
     <row r="7" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C7" s="7">
         <v>364</v>
@@ -17001,10 +22139,10 @@
     </row>
     <row r="8" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C8" s="7">
         <v>92</v>
@@ -17012,10 +22150,10 @@
     </row>
     <row r="9" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C9" s="7">
         <v>155</v>
@@ -17023,10 +22161,10 @@
     </row>
     <row r="10" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C10" s="7">
         <v>813</v>
@@ -17034,10 +22172,10 @@
     </row>
     <row r="11" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C11" s="7">
         <v>834</v>
@@ -17045,10 +22183,10 @@
     </row>
     <row r="12" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C12" s="7">
         <v>194</v>
@@ -17056,10 +22194,10 @@
     </row>
     <row r="13" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C13" s="7">
         <v>1060</v>
@@ -17067,10 +22205,10 @@
     </row>
     <row r="14" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C14" s="7">
         <v>1338</v>
@@ -17078,10 +22216,10 @@
     </row>
     <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C15" s="7">
         <v>1417</v>
@@ -17089,10 +22227,10 @@
     </row>
     <row r="16" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C16" s="7">
         <v>122</v>
@@ -17100,10 +22238,10 @@
     </row>
     <row r="17" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C17" s="7">
         <v>1381</v>
@@ -17111,10 +22249,10 @@
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C18" s="7">
         <v>787</v>
@@ -17122,10 +22260,10 @@
     </row>
     <row r="19" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C19" s="7">
         <v>720</v>
@@ -17133,10 +22271,10 @@
     </row>
     <row r="20" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C20" s="7">
         <v>710</v>
@@ -17144,10 +22282,10 @@
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C21" s="7">
         <v>723</v>
@@ -17155,10 +22293,10 @@
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C22" s="7">
         <v>811</v>
@@ -17166,10 +22304,10 @@
     </row>
     <row r="23" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C23" s="7">
         <v>96</v>
@@ -17177,10 +22315,10 @@
     </row>
     <row r="24" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C24" s="7">
         <v>1054</v>
@@ -17188,10 +22326,10 @@
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C25" s="7">
         <v>852</v>
@@ -17199,10 +22337,10 @@
     </row>
     <row r="26" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C26" s="7">
         <v>133</v>
@@ -17210,10 +22348,10 @@
     </row>
     <row r="27" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C27" s="7">
         <v>603</v>
@@ -17221,10 +22359,10 @@
     </row>
     <row r="28" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C28" s="7">
         <v>455</v>
@@ -17232,10 +22370,10 @@
     </row>
     <row r="29" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C29" s="7">
         <v>438</v>
@@ -17243,10 +22381,10 @@
     </row>
     <row r="30" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C30" s="7">
         <v>1043</v>
@@ -17254,10 +22392,10 @@
     </row>
     <row r="31" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C31" s="7">
         <v>394</v>
@@ -17265,10 +22403,10 @@
     </row>
     <row r="32" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C32" s="7">
         <v>683</v>
@@ -17276,10 +22414,10 @@
     </row>
     <row r="33" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C33" s="7">
         <v>687</v>
@@ -17287,10 +22425,10 @@
     </row>
     <row r="34" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C34" s="7">
         <v>533</v>
@@ -17298,10 +22436,10 @@
     </row>
     <row r="35" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C35" s="7">
         <v>844</v>
@@ -17309,10 +22447,10 @@
     </row>
     <row r="36" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C36" s="7">
         <v>775</v>
@@ -17320,19 +22458,19 @@
     </row>
     <row r="37" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C37" s="7"/>
     </row>
     <row r="38" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C38" s="7">
         <v>100</v>
@@ -17340,10 +22478,10 @@
     </row>
     <row r="39" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C39" s="7">
         <v>1102</v>
@@ -17351,10 +22489,10 @@
     </row>
     <row r="40" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C40" s="7">
         <v>340</v>
@@ -17362,10 +22500,10 @@
     </row>
     <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C41" s="7">
         <v>2326</v>
@@ -17373,10 +22511,10 @@
     </row>
     <row r="42" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C42" s="7">
         <v>1336</v>
@@ -17384,10 +22522,10 @@
     </row>
     <row r="43" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C43" s="7">
         <v>1167</v>
@@ -17395,10 +22533,10 @@
     </row>
     <row r="44" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C44" s="7">
         <v>183</v>
@@ -17406,10 +22544,10 @@
     </row>
     <row r="45" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C45" s="7">
         <v>54</v>
@@ -17417,10 +22555,10 @@
     </row>
     <row r="46" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C46" s="7">
         <v>328</v>
@@ -17428,10 +22566,10 @@
     </row>
     <row r="47" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C47" s="7">
         <v>2168</v>
@@ -17439,10 +22577,10 @@
     </row>
     <row r="48" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C48" s="7">
         <v>1492</v>
@@ -17450,10 +22588,10 @@
     </row>
     <row r="49" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C49" s="7">
         <v>386</v>
@@ -17461,10 +22599,10 @@
     </row>
     <row r="50" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C50" s="7">
         <v>160</v>
@@ -17472,10 +22610,10 @@
     </row>
     <row r="51" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C51" s="7">
         <v>1386</v>
@@ -17483,10 +22621,10 @@
     </row>
     <row r="52" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C52" s="7">
         <v>225</v>
@@ -17494,10 +22632,10 @@
     </row>
     <row r="53" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C53" s="7">
         <v>264</v>
@@ -17505,10 +22643,10 @@
     </row>
     <row r="54" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C54" s="7">
         <v>354</v>
@@ -17516,10 +22654,10 @@
     </row>
     <row r="55" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C55" s="7">
         <v>1252</v>
@@ -17527,10 +22665,10 @@
     </row>
     <row r="56" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C56" s="7">
         <v>64</v>
@@ -17538,10 +22676,10 @@
     </row>
     <row r="57" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C57" s="7">
         <v>329</v>
@@ -17549,10 +22687,10 @@
     </row>
     <row r="58" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C58" s="7">
         <v>444</v>
@@ -17560,10 +22698,10 @@
     </row>
     <row r="59" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C59" s="7">
         <v>334</v>
@@ -17571,10 +22709,10 @@
     </row>
     <row r="60" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C60" s="7">
         <v>320</v>
@@ -17582,10 +22720,10 @@
     </row>
     <row r="61" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="C61" s="7">
         <v>793</v>
@@ -17593,10 +22731,10 @@
     </row>
     <row r="62" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C62" s="7">
         <v>816</v>
@@ -17604,10 +22742,10 @@
     </row>
     <row r="63" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C63" s="7">
         <v>1266</v>
@@ -17615,10 +22753,10 @@
     </row>
     <row r="64" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="C64" s="7">
         <v>780</v>
@@ -17626,10 +22764,10 @@
     </row>
     <row r="65" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C65" s="7">
         <v>375</v>
@@ -17637,10 +22775,10 @@
     </row>
     <row r="66" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C66" s="7">
         <v>692</v>
@@ -17648,10 +22786,10 @@
     </row>
     <row r="67" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C67" s="7">
         <v>576</v>
@@ -17659,10 +22797,10 @@
     </row>
     <row r="68" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="C68" s="7">
         <v>313</v>
@@ -17670,10 +22808,10 @@
     </row>
     <row r="69" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="C69" s="7">
         <v>2307</v>
@@ -17681,10 +22819,10 @@
     </row>
     <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="C70" s="7">
         <v>808</v>
@@ -17692,10 +22830,10 @@
     </row>
     <row r="71" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="C71" s="7">
         <v>455</v>
@@ -17703,10 +22841,10 @@
     </row>
     <row r="72" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C72" s="7">
         <v>719</v>
@@ -17714,10 +22852,10 @@
     </row>
     <row r="73" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="C73" s="7">
         <v>699</v>
@@ -17725,10 +22863,10 @@
     </row>
     <row r="74" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="C74" s="7">
         <v>488</v>
@@ -17736,10 +22874,10 @@
     </row>
     <row r="75" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C75" s="7">
         <v>673</v>
@@ -17747,10 +22885,10 @@
     </row>
     <row r="76" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C76" s="7">
         <v>10</v>
@@ -17758,10 +22896,10 @@
     </row>
     <row r="77" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="C77" s="7">
         <v>1095</v>
@@ -17769,10 +22907,10 @@
     </row>
     <row r="78" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="C78" s="7">
         <v>680</v>
@@ -17780,10 +22918,10 @@
     </row>
     <row r="79" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C79" s="7">
         <v>960</v>
@@ -17791,10 +22929,10 @@
     </row>
     <row r="80" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C80" s="7">
         <v>888</v>
@@ -17802,10 +22940,10 @@
     </row>
     <row r="81" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C81" s="7">
         <v>370</v>
@@ -17813,10 +22951,10 @@
     </row>
     <row r="82" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C82" s="7">
         <v>716</v>
@@ -17824,19 +22962,19 @@
     </row>
     <row r="83" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C83" s="7"/>
     </row>
     <row r="84" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C84" s="7">
         <v>121</v>
@@ -17844,10 +22982,10 @@
     </row>
     <row r="85" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="C85" s="7">
         <v>1479</v>
@@ -17855,10 +22993,10 @@
     </row>
     <row r="86" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="C86" s="7">
         <v>485</v>
@@ -17866,10 +23004,10 @@
     </row>
     <row r="87" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="C87" s="7">
         <v>1511</v>
@@ -17877,10 +23015,10 @@
     </row>
     <row r="88" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C88" s="7">
         <v>484</v>
@@ -17888,10 +23026,10 @@
     </row>
     <row r="89" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="C89" s="7">
         <v>90</v>
@@ -17899,10 +23037,10 @@
     </row>
     <row r="90" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="C90" s="7">
         <v>913</v>
@@ -17910,10 +23048,10 @@
     </row>
     <row r="91" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="C91" s="7">
         <v>1536</v>
@@ -17921,10 +23059,10 @@
     </row>
     <row r="92" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="C92" s="7">
         <v>2480</v>
@@ -17932,10 +23070,10 @@
     </row>
     <row r="93" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C93" s="7">
         <v>685</v>
@@ -17943,10 +23081,10 @@
     </row>
     <row r="94" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="C94" s="7">
         <v>1439</v>
@@ -17954,10 +23092,10 @@
     </row>
     <row r="95" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C95" s="7">
         <v>2315</v>
@@ -17965,10 +23103,10 @@
     </row>
     <row r="96" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="C96" s="7">
         <v>193</v>
@@ -17976,10 +23114,10 @@
     </row>
     <row r="97" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="C97" s="7">
         <v>765</v>
@@ -17987,10 +23125,10 @@
     </row>
     <row r="98" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C98" s="7">
         <v>664</v>
@@ -17998,10 +23136,10 @@
     </row>
     <row r="99" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C99" s="7">
         <v>2377</v>
@@ -18009,10 +23147,10 @@
     </row>
     <row r="100" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C100" s="7">
         <v>878</v>
@@ -18020,10 +23158,10 @@
     </row>
     <row r="101" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="C101" s="7">
         <v>940</v>
@@ -18031,10 +23169,10 @@
     </row>
     <row r="102" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="C102" s="7">
         <v>1315</v>
@@ -18042,10 +23180,10 @@
     </row>
     <row r="103" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="C103" s="7">
         <v>39</v>
@@ -18053,10 +23191,10 @@
     </row>
     <row r="104" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="C104" s="7">
         <v>709</v>
@@ -18064,10 +23202,10 @@
     </row>
     <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C105" s="7">
         <v>874</v>
@@ -18075,10 +23213,10 @@
     </row>
     <row r="106" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C106" s="7">
         <v>1161</v>
@@ -18086,10 +23224,10 @@
     </row>
     <row r="107" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C107" s="7">
         <v>278</v>
@@ -18097,10 +23235,10 @@
     </row>
     <row r="108" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C108" s="7">
         <v>635</v>
@@ -18108,10 +23246,10 @@
     </row>
     <row r="109" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="C109" s="7">
         <v>677</v>
@@ -18119,10 +23257,10 @@
     </row>
     <row r="110" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="C110" s="7">
         <v>647</v>
@@ -18130,10 +23268,10 @@
     </row>
     <row r="111" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="C111" s="7">
         <v>148</v>
@@ -18141,10 +23279,10 @@
     </row>
     <row r="112" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="C112" s="7">
         <v>624</v>
@@ -18152,10 +23290,10 @@
     </row>
     <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="C113" s="7">
         <v>166</v>
@@ -18163,10 +23301,10 @@
     </row>
     <row r="114" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C114" s="7">
         <v>521</v>
@@ -18174,10 +23312,10 @@
     </row>
     <row r="115" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C115" s="7">
         <v>694</v>
@@ -18185,10 +23323,10 @@
     </row>
     <row r="116" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="C116" s="7">
         <v>297</v>
@@ -18196,10 +23334,10 @@
     </row>
     <row r="117" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C117" s="7">
         <v>427</v>
@@ -18207,10 +23345,10 @@
     </row>
     <row r="118" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="C118" s="7">
         <v>149</v>
@@ -18218,10 +23356,10 @@
     </row>
     <row r="119" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C119" s="7">
         <v>143</v>
@@ -18229,10 +23367,10 @@
     </row>
     <row r="120" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="C120" s="7">
         <v>156</v>
@@ -18240,10 +23378,10 @@
     </row>
     <row r="121" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="C121" s="7">
         <v>735</v>
@@ -18251,10 +23389,10 @@
     </row>
     <row r="122" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C122" s="7">
         <v>822</v>
@@ -18262,10 +23400,10 @@
     </row>
     <row r="123" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C123" s="7">
         <v>284</v>
@@ -18273,10 +23411,10 @@
     </row>
     <row r="124" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C124" s="7">
         <v>582</v>
@@ -18284,10 +23422,10 @@
     </row>
     <row r="125" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C125" s="7">
         <v>94</v>
@@ -18295,19 +23433,19 @@
     </row>
     <row r="126" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C126" s="7"/>
     </row>
     <row r="127" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="C127" s="7">
         <v>2506</v>
@@ -18315,10 +23453,10 @@
     </row>
     <row r="128" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="C128" s="7">
         <v>1069</v>
@@ -18326,10 +23464,10 @@
     </row>
     <row r="129" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C129" s="7">
         <v>165</v>
@@ -18337,10 +23475,10 @@
     </row>
     <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="C130" s="7">
         <v>378</v>
@@ -18348,10 +23486,10 @@
     </row>
     <row r="131" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C131" s="7">
         <v>764</v>
@@ -18359,10 +23497,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C132" s="7">
         <v>260</v>
@@ -18370,10 +23508,10 @@
     </row>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="C133" s="7">
         <v>1281</v>
@@ -18381,10 +23519,10 @@
     </row>
     <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="C134" s="7">
         <v>695</v>
@@ -18392,10 +23530,10 @@
     </row>
     <row r="135" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="C135" s="7">
         <v>712</v>
@@ -18403,10 +23541,10 @@
     </row>
     <row r="136" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="C136" s="7">
         <v>2025</v>
@@ -18414,10 +23552,10 @@
     </row>
     <row r="137" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C137" s="7">
         <v>722</v>
@@ -18425,10 +23563,10 @@
     </row>
     <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C138" s="7">
         <v>733</v>
@@ -18436,10 +23574,10 @@
     </row>
     <row r="139" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C139" s="7">
         <v>2411</v>
@@ -18447,10 +23585,10 @@
     </row>
     <row r="140" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C140" s="7">
         <v>272</v>
@@ -18458,10 +23596,10 @@
     </row>
     <row r="141" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C141" s="7">
         <v>1180</v>
@@ -18469,19 +23607,19 @@
     </row>
     <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C142" s="7"/>
     </row>
     <row r="143" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C143" s="7">
         <v>838</v>
@@ -18489,10 +23627,10 @@
     </row>
     <row r="144" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C144" s="7">
         <v>527</v>
@@ -18503,7 +23641,7 @@
         <v>718</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C145" s="7">
         <v>1761</v>
@@ -18511,10 +23649,10 @@
     </row>
     <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C146" s="7">
         <v>1409</v>
@@ -18522,10 +23660,10 @@
     </row>
     <row r="147" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C147" s="7">
         <v>1050</v>
@@ -18533,10 +23671,10 @@
     </row>
     <row r="148" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C148" s="7">
         <v>557</v>
@@ -18544,10 +23682,10 @@
     </row>
     <row r="149" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C149" s="7">
         <v>776</v>
@@ -18555,19 +23693,19 @@
     </row>
     <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C150" s="7"/>
     </row>
     <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C151" s="7">
         <v>188</v>
@@ -18575,10 +23713,10 @@
     </row>
     <row r="152" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C152" s="7">
         <v>1531</v>
@@ -18586,19 +23724,19 @@
     </row>
     <row r="153" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="C153" s="7"/>
     </row>
     <row r="154" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="C154" s="7">
         <v>943</v>
@@ -18606,28 +23744,28 @@
     </row>
     <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C155" s="7"/>
     </row>
     <row r="156" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C156" s="7"/>
     </row>
     <row r="157" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C157" s="7"/>
     </row>

--- a/data/lookup/bmf_code_lookup.xlsx
+++ b/data/lookup/bmf_code_lookup.xlsx
@@ -17,18 +17,18 @@
     <sheet name="parent_organization" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="subsection_classification_code" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="affiliation_code" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="foundation_code" sheetId="13" state="visible" r:id="rId12"/>
-    <sheet name="organization_code" sheetId="14" state="visible" r:id="rId13"/>
-    <sheet name="activity_code" sheetId="15" state="visible" r:id="rId14"/>
-    <sheet name="deductibility_code" sheetId="12" state="visible" r:id="rId15"/>
-    <sheet name="nteev2_subsector" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="organization_code" sheetId="14" state="visible" r:id="rId12"/>
+    <sheet name="activity_code" sheetId="15" state="visible" r:id="rId13"/>
+    <sheet name="deductibility_code" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="nteev2_subsector" sheetId="16" state="visible" r:id="rId15"/>
+    <sheet name="foundation_code" sheetId="17" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="2131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="2154">
   <si>
     <t>status_code</t>
   </si>
@@ -6427,6 +6427,75 @@
   </si>
   <si>
     <t xml:space="preserve">Hospitals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foundation_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foundation_code_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foundation_code_effective_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All organizations except 501(c)(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private operating foundation exempt from payment of section 4940 taxes on investment income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private operating foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private non-operating foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undocumented (not in IRS BMF Extract Information sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suspense (a specific type not identified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Church—IRC Section 170(b)(1)(A)(i)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School—IRC Section 170(b)(1)(A)(ii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital—IRC Section 170(b)(1)(A)(iii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizations operated for the benefit of a college or university—IRC Section 170(b)(1)(A)(iv)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal, State or local government unit—IRC Section 170(b)(1)(A)(v)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organization receiving support from governmental unit or general public—IRC Section 170(b)(1)(A)(vi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General, public charity—IRC Section 509(a)(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public charity supporting (FC 09–15)—IRC Section 509(a)(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public safety—IRC Section 509(a)(4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supporting organization - IRC 509(a)(3) - Type I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supporting organization - IRC 509(a)(3) - Type II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supporting organization - IRC 509(a)(3) - Type III functionally integrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supporting organization - IRC 509(a)(3) - Type III not functionally integrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture research organization 170(b)(1)(A)(ix)</t>
   </si>
 </sst>
 </file>
@@ -6451,8 +6520,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <b/>
     </font>
   </fonts>
@@ -8291,13 +8358,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1679</v>
+        <v>1699</v>
       </c>
       <c r="B1" t="s">
-        <v>1680</v>
+        <v>1700</v>
       </c>
       <c r="C1" t="s">
-        <v>1681</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="2">
@@ -8305,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1650</v>
+        <v>1702</v>
       </c>
       <c r="C2" t="n">
         <v>20241213</v>
@@ -8313,10 +8380,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1682</v>
+        <v>1703</v>
       </c>
       <c r="C3" t="n">
         <v>20241213</v>
@@ -8324,10 +8391,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1683</v>
+        <v>1704</v>
       </c>
       <c r="C4" t="n">
         <v>20241213</v>
@@ -8335,10 +8402,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1684</v>
+        <v>1705</v>
       </c>
       <c r="C5" t="n">
         <v>20241213</v>
@@ -8346,10 +8413,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1685</v>
+        <v>1706</v>
       </c>
       <c r="C6" t="n">
         <v>20241213</v>
@@ -8357,10 +8424,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1686</v>
+        <v>1707</v>
       </c>
       <c r="C7" t="n">
         <v>20241213</v>
@@ -8368,133 +8435,12 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1687</v>
+        <v>1708</v>
       </c>
       <c r="C8" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1688</v>
-      </c>
-      <c r="C9" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C10" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1690</v>
-      </c>
-      <c r="C11" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C12" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C13" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C14" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C15" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C16" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C17" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1697</v>
-      </c>
-      <c r="C18" t="n">
-        <v>20241213</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C19" t="n">
         <v>20241213</v>
       </c>
     </row>
@@ -8511,90 +8457,3515 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="B1" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
       <c r="C1" t="s">
-        <v>1701</v>
+        <v>1711</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1712</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>1702</v>
       </c>
-      <c r="C2" t="n">
-        <v>20241213</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1703</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20241213</v>
+      <c r="A3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1716</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1704</v>
-      </c>
-      <c r="C4" t="n">
-        <v>20241213</v>
+      <c r="A4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1718</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1705</v>
-      </c>
-      <c r="C5" t="n">
-        <v>20241213</v>
+      <c r="A5" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1720</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1706</v>
-      </c>
-      <c r="C6" t="n">
-        <v>20241213</v>
+      <c r="A6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1722</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="C7" t="n">
-        <v>20241213</v>
+      <c r="A7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1724</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1708</v>
-      </c>
-      <c r="C8" t="n">
-        <v>20241213</v>
+      <c r="A8" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B12" t="n">
+        <v>918</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B32" t="n">
+        <v>574</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B33" t="n">
+        <v>602</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B34" t="n">
+        <v>914</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B35" t="n">
+        <v>918</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B36" t="n">
+        <v>299</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B51" t="n">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B52" t="n">
+        <v>914</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B53" t="n">
+        <v>561</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B54" t="n">
+        <v>602</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B55" t="n">
+        <v>120</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B56" t="n">
+        <v>121</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B57" t="n">
+        <v>122</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B58" t="n">
+        <v>123</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B59" t="n">
+        <v>124</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B60" t="n">
+        <v>125</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B61" t="n">
+        <v>126</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B62" t="n">
+        <v>149</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B63" t="n">
+        <v>299</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B65" t="n">
+        <v>151</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B66" t="n">
+        <v>152</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B67" t="n">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B68" t="n">
+        <v>155</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B69" t="n">
+        <v>156</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B70" t="n">
+        <v>157</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B71" t="n">
+        <v>158</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B72" t="n">
+        <v>159</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B73" t="n">
+        <v>160</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B74" t="n">
+        <v>161</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B75" t="n">
+        <v>162</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B76" t="n">
+        <v>163</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B77" t="n">
+        <v>164</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B78" t="n">
+        <v>165</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B79" t="n">
+        <v>166</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B80" t="n">
+        <v>167</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B81" t="n">
+        <v>168</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B82" t="n">
+        <v>169</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B83" t="n">
+        <v>179</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B84" t="n">
+        <v>180</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B85" t="n">
+        <v>181</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B86" t="n">
+        <v>199</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B87" t="n">
+        <v>161</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B88" t="n">
+        <v>200</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B89" t="n">
+        <v>201</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B90" t="n">
+        <v>202</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B91" t="n">
+        <v>203</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B92" t="n">
+        <v>204</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B93" t="n">
+        <v>205</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B94" t="n">
+        <v>206</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B95" t="n">
+        <v>207</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B96" t="n">
+        <v>208</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B97" t="n">
+        <v>209</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B98" t="n">
+        <v>210</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B99" t="n">
+        <v>211</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B100" t="n">
+        <v>212</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B101" t="n">
+        <v>213</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B102" t="n">
+        <v>229</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B103" t="n">
+        <v>905</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B104" t="n">
+        <v>403</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B105" t="n">
+        <v>120</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B107" t="n">
+        <v>230</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B108" t="n">
+        <v>231</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B109" t="n">
+        <v>232</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B110" t="n">
+        <v>233</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B111" t="n">
+        <v>234</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B112" t="n">
+        <v>235</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B113" t="n">
+        <v>237</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B114" t="n">
+        <v>249</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B115" t="n">
+        <v>322</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B117" t="n">
+        <v>250</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B118" t="n">
+        <v>251</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B119" t="n">
+        <v>252</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B120" t="n">
+        <v>253</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B121" t="n">
+        <v>254</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B122" t="n">
+        <v>259</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B123" t="n">
+        <v>234</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B124" t="n">
+        <v>157</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B125" t="n">
+        <v>260</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B126" t="n">
+        <v>261</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B127" t="n">
+        <v>262</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B128" t="n">
+        <v>263</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B129" t="n">
+        <v>264</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B130" t="n">
+        <v>265</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B131" t="n">
+        <v>266</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B132" t="n">
+        <v>267</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B133" t="n">
+        <v>268</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B134" t="n">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B135" t="n">
+        <v>279</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B136" t="n">
+        <v>280</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B137" t="n">
+        <v>281</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B138" t="n">
+        <v>282</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B139" t="n">
+        <v>283</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B140" t="n">
+        <v>284</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B141" t="n">
+        <v>285</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B142" t="n">
+        <v>286</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B143" t="n">
+        <v>287</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B144" t="n">
+        <v>288</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B145" t="n">
+        <v>296</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B146" t="n">
+        <v>297</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B147" t="n">
+        <v>298</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B148" t="n">
+        <v>299</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B149" t="n">
+        <v>300</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B150" t="n">
+        <v>301</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B151" t="n">
+        <v>317</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B152" t="n">
+        <v>318</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B153" t="n">
+        <v>319</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B154" t="n">
+        <v>356</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B155" t="n">
+        <v>321</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B157" t="n">
+        <v>320</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B158" t="n">
+        <v>321</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B159" t="n">
+        <v>322</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B160" t="n">
+        <v>324</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B161" t="n">
+        <v>325</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B162" t="n">
+        <v>326</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B163" t="n">
+        <v>327</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B164" t="n">
+        <v>328</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B165" t="n">
+        <v>349</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B166" t="n">
+        <v>350</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B167" t="n">
+        <v>351</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B168" t="n">
+        <v>352</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B169" t="n">
+        <v>353</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B170" t="n">
+        <v>354</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B171" t="n">
+        <v>355</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B172" t="n">
+        <v>356</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B173" t="n">
+        <v>379</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B175" t="n">
+        <v>402</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B176" t="n">
+        <v>380</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B177" t="n">
+        <v>381</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B178" t="n">
+        <v>382</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B179" t="n">
+        <v>398</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B180" t="n">
+        <v>399</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B181" t="n">
+        <v>152</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B183" t="n">
+        <v>326</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B184" t="n">
+        <v>400</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B185" t="n">
+        <v>401</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B186" t="n">
+        <v>402</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B187" t="n">
+        <v>403</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B188" t="n">
+        <v>404</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B189" t="n">
+        <v>405</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B190" t="n">
+        <v>406</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B191" t="n">
+        <v>407</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B192" t="n">
+        <v>408</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B193" t="n">
+        <v>429</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B194" t="n">
+        <v>297</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B195" t="n">
+        <v>296</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B196" t="n">
+        <v>566</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B197" t="n">
+        <v>574</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B198" t="n">
+        <v>569</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B199" t="n">
+        <v>462</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B200" t="n">
+        <v>158</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B201" t="n">
+        <v>430</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B202" t="n">
+        <v>431</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B203" t="n">
+        <v>432</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B204" t="n">
+        <v>449</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B205" t="n">
+        <v>460</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B206" t="n">
+        <v>461</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B207" t="n">
+        <v>462</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B208" t="n">
+        <v>463</v>
+      </c>
+      <c r="C208" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B209" t="n">
+        <v>465</v>
+      </c>
+      <c r="C209" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B210" t="n">
+        <v>480</v>
+      </c>
+      <c r="C210" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B211" t="n">
+        <v>481</v>
+      </c>
+      <c r="C211" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B212" t="n">
+        <v>482</v>
+      </c>
+      <c r="C212" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B213" t="n">
+        <v>483</v>
+      </c>
+      <c r="C213" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B214" t="n">
+        <v>484</v>
+      </c>
+      <c r="C214" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B215" t="n">
+        <v>509</v>
+      </c>
+      <c r="C215" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B216" t="n">
+        <v>510</v>
+      </c>
+      <c r="C216" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B217" t="n">
+        <v>511</v>
+      </c>
+      <c r="C217" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B218" t="n">
+        <v>512</v>
+      </c>
+      <c r="C218" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B219" t="n">
+        <v>513</v>
+      </c>
+      <c r="C219" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B220" t="n">
+        <v>514</v>
+      </c>
+      <c r="C220" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B221" t="n">
+        <v>515</v>
+      </c>
+      <c r="C221" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B222" t="n">
+        <v>516</v>
+      </c>
+      <c r="C222" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B223" t="n">
+        <v>517</v>
+      </c>
+      <c r="C223" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B224" t="n">
+        <v>518</v>
+      </c>
+      <c r="C224" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B225" t="n">
+        <v>519</v>
+      </c>
+      <c r="C225" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B226" t="n">
+        <v>520</v>
+      </c>
+      <c r="C226" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B227" t="n">
+        <v>521</v>
+      </c>
+      <c r="C227" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B228" t="n">
+        <v>522</v>
+      </c>
+      <c r="C228" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B229" t="n">
+        <v>523</v>
+      </c>
+      <c r="C229" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B230" t="n">
+        <v>524</v>
+      </c>
+      <c r="C230" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B231" t="n">
+        <v>525</v>
+      </c>
+      <c r="C231" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B232" t="n">
+        <v>526</v>
+      </c>
+      <c r="C232" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B233" t="n">
+        <v>527</v>
+      </c>
+      <c r="C233" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B234" t="n">
+        <v>528</v>
+      </c>
+      <c r="C234" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B235" t="n">
+        <v>529</v>
+      </c>
+      <c r="C235" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B236" t="n">
+        <v>530</v>
+      </c>
+      <c r="C236" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B237" t="n">
+        <v>531</v>
+      </c>
+      <c r="C237" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B238" t="n">
+        <v>532</v>
+      </c>
+      <c r="C238" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B239" t="n">
+        <v>533</v>
+      </c>
+      <c r="C239" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B240" t="n">
+        <v>534</v>
+      </c>
+      <c r="C240" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B241" t="n">
+        <v>535</v>
+      </c>
+      <c r="C241" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B242" t="n">
+        <v>536</v>
+      </c>
+      <c r="C242" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B243" t="n">
+        <v>537</v>
+      </c>
+      <c r="C243" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B244" t="n">
+        <v>538</v>
+      </c>
+      <c r="C244" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B245" t="n">
+        <v>539</v>
+      </c>
+      <c r="C245" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B246" t="n">
+        <v>540</v>
+      </c>
+      <c r="C246" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B247" t="n">
+        <v>541</v>
+      </c>
+      <c r="C247" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B248" t="n">
+        <v>542</v>
+      </c>
+      <c r="C248" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B249" t="n">
+        <v>543</v>
+      </c>
+      <c r="C249" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B250" t="n">
+        <v>559</v>
+      </c>
+      <c r="C250" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B251" t="n">
+        <v>560</v>
+      </c>
+      <c r="C251" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B252" t="n">
+        <v>561</v>
+      </c>
+      <c r="C252" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B253" t="n">
+        <v>562</v>
+      </c>
+      <c r="C253" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B254" t="n">
+        <v>563</v>
+      </c>
+      <c r="C254" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B255" t="n">
+        <v>564</v>
+      </c>
+      <c r="C255" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B256" t="n">
+        <v>565</v>
+      </c>
+      <c r="C256" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B257" t="n">
+        <v>566</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B258" t="n">
+        <v>567</v>
+      </c>
+      <c r="C258" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B259" t="n">
+        <v>568</v>
+      </c>
+      <c r="C259" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B260" t="n">
+        <v>569</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B261" t="n">
+        <v>572</v>
+      </c>
+      <c r="C261" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B262" t="n">
+        <v>573</v>
+      </c>
+      <c r="C262" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B263" t="n">
+        <v>574</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B264" t="n">
+        <v>575</v>
+      </c>
+      <c r="C264" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D264" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D265" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D266" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D267" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C268" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D268" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B269" t="n">
+        <v>600</v>
+      </c>
+      <c r="C269" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B270" t="n">
+        <v>601</v>
+      </c>
+      <c r="C270" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B271" t="n">
+        <v>602</v>
+      </c>
+      <c r="C271" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B272" t="n">
+        <v>603</v>
+      </c>
+      <c r="C272" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B273" t="n">
+        <v>900</v>
+      </c>
+      <c r="C273" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B274" t="n">
+        <v>901</v>
+      </c>
+      <c r="C274" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B275" t="n">
+        <v>902</v>
+      </c>
+      <c r="C275" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B276" t="n">
+        <v>903</v>
+      </c>
+      <c r="C276" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B277" t="n">
+        <v>904</v>
+      </c>
+      <c r="C277" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D277" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B278" t="n">
+        <v>905</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B279" t="n">
+        <v>906</v>
+      </c>
+      <c r="C279" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B280" t="n">
+        <v>907</v>
+      </c>
+      <c r="C280" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B281" t="n">
+        <v>908</v>
+      </c>
+      <c r="C281" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B282" t="n">
+        <v>909</v>
+      </c>
+      <c r="C282" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B283" t="n">
+        <v>910</v>
+      </c>
+      <c r="C283" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B284" t="n">
+        <v>911</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B285" t="n">
+        <v>912</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B286" t="n">
+        <v>913</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B287" t="n">
+        <v>914</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B288" t="n">
+        <v>915</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B289" t="n">
+        <v>916</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B290" t="n">
+        <v>917</v>
+      </c>
+      <c r="C290" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B291" t="n">
+        <v>918</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B292" t="n">
+        <v>919</v>
+      </c>
+      <c r="C292" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B293" t="n">
+        <v>920</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B294" t="n">
+        <v>921</v>
+      </c>
+      <c r="C294" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B295" t="n">
+        <v>922</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B296" t="n">
+        <v>923</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B297" t="n">
+        <v>924</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B298" t="n">
+        <v>925</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B299" t="n">
+        <v>926</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B300" t="n">
+        <v>928</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B301" t="n">
+        <v>930</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B302" t="n">
+        <v>931</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B303" t="n">
+        <v>990</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B304" t="n">
+        <v>994</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B305" t="n">
+        <v>995</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B306" t="n">
+        <v>998</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2102</v>
       </c>
     </row>
   </sheetData>
@@ -8610,3515 +11981,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1709</v>
+        <v>1671</v>
       </c>
       <c r="B1" t="s">
-        <v>1710</v>
+        <v>1672</v>
       </c>
       <c r="C1" t="s">
-        <v>1711</v>
+        <v>1673</v>
       </c>
       <c r="D1" t="s">
-        <v>1712</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1717</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>1719</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1721</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>1727</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>1731</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B12" t="n">
-        <v>918</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1733</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>1735</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1736</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>1739</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1742</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>1747</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>1749</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>1751</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1752</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>1754</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>1756</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>1758</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>1760</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1763</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>1766</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>1768</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1769</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>1770</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>1772</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B32" t="n">
-        <v>574</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B33" t="n">
-        <v>602</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1778</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B34" t="n">
-        <v>914</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1780</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B35" t="n">
-        <v>918</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1782</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B36" t="n">
-        <v>299</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1783</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>1789</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>1793</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>1795</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>1797</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>1799</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>1803</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1804</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>1807</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>1809</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>1811</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>1735</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B51" t="n">
-        <v>119</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B52" t="n">
-        <v>914</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1814</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B53" t="n">
-        <v>561</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1816</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B54" t="n">
-        <v>602</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B55" t="n">
-        <v>120</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B56" t="n">
-        <v>121</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B57" t="n">
-        <v>122</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B58" t="n">
-        <v>123</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1822</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B59" t="n">
-        <v>124</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B60" t="n">
-        <v>125</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1824</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B61" t="n">
-        <v>126</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B62" t="n">
-        <v>149</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B63" t="n">
-        <v>299</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B64" t="n">
-        <v>150</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B65" t="n">
-        <v>151</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B66" t="n">
-        <v>152</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B67" t="n">
-        <v>153</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B68" t="n">
-        <v>155</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1835</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B69" t="n">
-        <v>156</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B70" t="n">
-        <v>157</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B71" t="n">
-        <v>158</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B72" t="n">
-        <v>159</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B73" t="n">
-        <v>160</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D73" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B74" t="n">
-        <v>161</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B75" t="n">
-        <v>162</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B76" t="n">
-        <v>163</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B77" t="n">
-        <v>164</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B78" t="n">
-        <v>165</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B79" t="n">
-        <v>166</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B80" t="n">
-        <v>167</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B81" t="n">
-        <v>168</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B82" t="n">
-        <v>169</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B83" t="n">
-        <v>179</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B84" t="n">
-        <v>180</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B85" t="n">
-        <v>181</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B86" t="n">
-        <v>199</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B87" t="n">
-        <v>161</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1841</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B88" t="n">
-        <v>200</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B89" t="n">
-        <v>201</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1858</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B90" t="n">
-        <v>202</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B91" t="n">
-        <v>203</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B92" t="n">
-        <v>204</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B93" t="n">
-        <v>205</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B94" t="n">
-        <v>206</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B95" t="n">
-        <v>207</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B96" t="n">
-        <v>208</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B97" t="n">
-        <v>209</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B98" t="n">
-        <v>210</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B99" t="n">
-        <v>211</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B100" t="n">
-        <v>212</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B101" t="n">
-        <v>213</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B102" t="n">
-        <v>229</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B103" t="n">
-        <v>905</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1872</v>
-      </c>
-      <c r="D103" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B104" t="n">
-        <v>403</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D104" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B105" t="n">
-        <v>120</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1819</v>
-      </c>
-      <c r="D105" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1877</v>
-      </c>
-      <c r="D106" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B107" t="n">
-        <v>230</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B108" t="n">
-        <v>231</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B109" t="n">
-        <v>232</v>
-      </c>
-      <c r="C109" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B110" t="n">
-        <v>233</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B111" t="n">
-        <v>234</v>
-      </c>
-      <c r="C111" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B112" t="n">
-        <v>235</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B113" t="n">
-        <v>237</v>
-      </c>
-      <c r="C113" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B114" t="n">
-        <v>249</v>
-      </c>
-      <c r="C114" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B115" t="n">
-        <v>322</v>
-      </c>
-      <c r="C115" t="s">
-        <v>1888</v>
-      </c>
-      <c r="D115" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B116" s="8" t="s">
-        <v>1799</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B117" t="n">
-        <v>250</v>
-      </c>
-      <c r="C117" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B118" t="n">
-        <v>251</v>
-      </c>
-      <c r="C118" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B119" t="n">
-        <v>252</v>
-      </c>
-      <c r="C119" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B120" t="n">
-        <v>253</v>
-      </c>
-      <c r="C120" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B121" t="n">
-        <v>254</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1896</v>
-      </c>
-      <c r="D121" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B122" t="n">
-        <v>259</v>
-      </c>
-      <c r="C122" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B123" t="n">
-        <v>234</v>
-      </c>
-      <c r="C123" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D123" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B124" t="n">
-        <v>157</v>
-      </c>
-      <c r="C124" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D124" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B125" t="n">
-        <v>260</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B126" t="n">
-        <v>261</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B127" t="n">
-        <v>262</v>
-      </c>
-      <c r="C127" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B128" t="n">
-        <v>263</v>
-      </c>
-      <c r="C128" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B129" t="n">
-        <v>264</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B130" t="n">
-        <v>265</v>
-      </c>
-      <c r="C130" t="s">
-        <v>1907</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B131" t="n">
-        <v>266</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B132" t="n">
-        <v>267</v>
-      </c>
-      <c r="C132" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B133" t="n">
-        <v>268</v>
-      </c>
-      <c r="C133" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B134" t="n">
-        <v>269</v>
-      </c>
-      <c r="C134" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B135" t="n">
-        <v>279</v>
-      </c>
-      <c r="C135" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B136" t="n">
-        <v>280</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B137" t="n">
-        <v>281</v>
-      </c>
-      <c r="C137" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B138" t="n">
-        <v>282</v>
-      </c>
-      <c r="C138" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B139" t="n">
-        <v>283</v>
-      </c>
-      <c r="C139" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B140" t="n">
-        <v>284</v>
-      </c>
-      <c r="C140" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B141" t="n">
-        <v>285</v>
-      </c>
-      <c r="C141" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B142" t="n">
-        <v>286</v>
-      </c>
-      <c r="C142" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B143" t="n">
-        <v>287</v>
-      </c>
-      <c r="C143" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B144" t="n">
-        <v>288</v>
-      </c>
-      <c r="C144" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B145" t="n">
-        <v>296</v>
-      </c>
-      <c r="C145" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B146" t="n">
-        <v>297</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B147" t="n">
-        <v>298</v>
-      </c>
-      <c r="C147" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B148" t="n">
-        <v>299</v>
-      </c>
-      <c r="C148" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B149" t="n">
-        <v>300</v>
-      </c>
-      <c r="C149" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B150" t="n">
-        <v>301</v>
-      </c>
-      <c r="C150" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B151" t="n">
-        <v>317</v>
-      </c>
-      <c r="C151" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B152" t="n">
-        <v>318</v>
-      </c>
-      <c r="C152" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B153" t="n">
-        <v>319</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B154" t="n">
-        <v>356</v>
-      </c>
-      <c r="C154" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D154" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B155" t="n">
-        <v>321</v>
-      </c>
-      <c r="C155" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B156" s="8" t="s">
-        <v>1756</v>
-      </c>
-      <c r="C156" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D156" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B157" t="n">
-        <v>320</v>
-      </c>
-      <c r="C157" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B158" t="n">
-        <v>321</v>
-      </c>
-      <c r="C158" t="s">
-        <v>1938</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B159" t="n">
-        <v>322</v>
-      </c>
-      <c r="C159" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B160" t="n">
-        <v>324</v>
-      </c>
-      <c r="C160" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B161" t="n">
-        <v>325</v>
-      </c>
-      <c r="C161" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B162" t="n">
-        <v>326</v>
-      </c>
-      <c r="C162" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B163" t="n">
-        <v>327</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B164" t="n">
-        <v>328</v>
-      </c>
-      <c r="C164" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B165" t="n">
-        <v>349</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B166" t="n">
-        <v>350</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B167" t="n">
-        <v>351</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B168" t="n">
-        <v>352</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B169" t="n">
-        <v>353</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B170" t="n">
-        <v>354</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B171" t="n">
-        <v>355</v>
-      </c>
-      <c r="C171" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B172" t="n">
-        <v>356</v>
-      </c>
-      <c r="C172" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B173" t="n">
-        <v>379</v>
-      </c>
-      <c r="C173" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B174" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D174" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B175" t="n">
-        <v>402</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D175" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B176" t="n">
-        <v>380</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B177" t="n">
-        <v>381</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B178" t="n">
-        <v>382</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D178" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B179" t="n">
-        <v>398</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B180" t="n">
-        <v>399</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B181" t="n">
-        <v>152</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1832</v>
-      </c>
-      <c r="D181" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C182" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D182" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B183" t="n">
-        <v>326</v>
-      </c>
-      <c r="C183" t="s">
-        <v>1968</v>
-      </c>
-      <c r="D183" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B184" t="n">
-        <v>400</v>
-      </c>
-      <c r="C184" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B185" t="n">
-        <v>401</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B186" t="n">
-        <v>402</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B187" t="n">
-        <v>403</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B188" t="n">
-        <v>404</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B189" t="n">
-        <v>405</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B190" t="n">
-        <v>406</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B191" t="n">
-        <v>407</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B192" t="n">
-        <v>408</v>
-      </c>
-      <c r="C192" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B193" t="n">
-        <v>429</v>
-      </c>
-      <c r="C193" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B194" t="n">
-        <v>297</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1981</v>
-      </c>
-      <c r="D194" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B195" t="n">
-        <v>296</v>
-      </c>
-      <c r="C195" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D195" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B196" t="n">
-        <v>566</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D196" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B197" t="n">
-        <v>574</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D197" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B198" t="n">
-        <v>569</v>
-      </c>
-      <c r="C198" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D198" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B199" t="n">
-        <v>462</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D199" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B200" t="n">
-        <v>158</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D200" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B201" t="n">
-        <v>430</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B202" t="n">
-        <v>431</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B203" t="n">
-        <v>432</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B204" t="n">
-        <v>449</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B205" t="n">
-        <v>460</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B206" t="n">
-        <v>461</v>
-      </c>
-      <c r="C206" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B207" t="n">
-        <v>462</v>
-      </c>
-      <c r="C207" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B208" t="n">
-        <v>463</v>
-      </c>
-      <c r="C208" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B209" t="n">
-        <v>465</v>
-      </c>
-      <c r="C209" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B210" t="n">
-        <v>480</v>
-      </c>
-      <c r="C210" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B211" t="n">
-        <v>481</v>
-      </c>
-      <c r="C211" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B212" t="n">
-        <v>482</v>
-      </c>
-      <c r="C212" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B213" t="n">
-        <v>483</v>
-      </c>
-      <c r="C213" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B214" t="n">
-        <v>484</v>
-      </c>
-      <c r="C214" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B215" t="n">
-        <v>509</v>
-      </c>
-      <c r="C215" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B216" t="n">
-        <v>510</v>
-      </c>
-      <c r="C216" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B217" t="n">
-        <v>511</v>
-      </c>
-      <c r="C217" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B218" t="n">
-        <v>512</v>
-      </c>
-      <c r="C218" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B219" t="n">
-        <v>513</v>
-      </c>
-      <c r="C219" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B220" t="n">
-        <v>514</v>
-      </c>
-      <c r="C220" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B221" t="n">
-        <v>515</v>
-      </c>
-      <c r="C221" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B222" t="n">
-        <v>516</v>
-      </c>
-      <c r="C222" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B223" t="n">
-        <v>517</v>
-      </c>
-      <c r="C223" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B224" t="n">
-        <v>518</v>
-      </c>
-      <c r="C224" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B225" t="n">
-        <v>519</v>
-      </c>
-      <c r="C225" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B226" t="n">
-        <v>520</v>
-      </c>
-      <c r="C226" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B227" t="n">
-        <v>521</v>
-      </c>
-      <c r="C227" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B228" t="n">
-        <v>522</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B229" t="n">
-        <v>523</v>
-      </c>
-      <c r="C229" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B230" t="n">
-        <v>524</v>
-      </c>
-      <c r="C230" t="s">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B231" t="n">
-        <v>525</v>
-      </c>
-      <c r="C231" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B232" t="n">
-        <v>526</v>
-      </c>
-      <c r="C232" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B233" t="n">
-        <v>527</v>
-      </c>
-      <c r="C233" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B234" t="n">
-        <v>528</v>
-      </c>
-      <c r="C234" t="s">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B235" t="n">
-        <v>529</v>
-      </c>
-      <c r="C235" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B236" t="n">
-        <v>530</v>
-      </c>
-      <c r="C236" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B237" t="n">
-        <v>531</v>
-      </c>
-      <c r="C237" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B238" t="n">
-        <v>532</v>
-      </c>
-      <c r="C238" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B239" t="n">
-        <v>533</v>
-      </c>
-      <c r="C239" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B240" t="n">
-        <v>534</v>
-      </c>
-      <c r="C240" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B241" t="n">
-        <v>535</v>
-      </c>
-      <c r="C241" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B242" t="n">
-        <v>536</v>
-      </c>
-      <c r="C242" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B243" t="n">
-        <v>537</v>
-      </c>
-      <c r="C243" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B244" t="n">
-        <v>538</v>
-      </c>
-      <c r="C244" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B245" t="n">
-        <v>539</v>
-      </c>
-      <c r="C245" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B246" t="n">
-        <v>540</v>
-      </c>
-      <c r="C246" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B247" t="n">
-        <v>541</v>
-      </c>
-      <c r="C247" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B248" t="n">
-        <v>542</v>
-      </c>
-      <c r="C248" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B249" t="n">
-        <v>543</v>
-      </c>
-      <c r="C249" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B250" t="n">
-        <v>559</v>
-      </c>
-      <c r="C250" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B251" t="n">
-        <v>560</v>
-      </c>
-      <c r="C251" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B252" t="n">
-        <v>561</v>
-      </c>
-      <c r="C252" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B253" t="n">
-        <v>562</v>
-      </c>
-      <c r="C253" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B254" t="n">
-        <v>563</v>
-      </c>
-      <c r="C254" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B255" t="n">
-        <v>564</v>
-      </c>
-      <c r="C255" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B256" t="n">
-        <v>565</v>
-      </c>
-      <c r="C256" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B257" t="n">
-        <v>566</v>
-      </c>
-      <c r="C257" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B258" t="n">
-        <v>567</v>
-      </c>
-      <c r="C258" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B259" t="n">
-        <v>568</v>
-      </c>
-      <c r="C259" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B260" t="n">
-        <v>569</v>
-      </c>
-      <c r="C260" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B261" t="n">
-        <v>572</v>
-      </c>
-      <c r="C261" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B262" t="n">
-        <v>573</v>
-      </c>
-      <c r="C262" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B263" t="n">
-        <v>574</v>
-      </c>
-      <c r="C263" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B264" t="n">
-        <v>575</v>
-      </c>
-      <c r="C264" t="s">
-        <v>2056</v>
-      </c>
-      <c r="D264" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B265" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C265" t="s">
-        <v>1759</v>
-      </c>
-      <c r="D265" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B266" s="8" t="s">
-        <v>1758</v>
-      </c>
-      <c r="C266" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D266" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B267" s="8" t="s">
-        <v>1760</v>
-      </c>
-      <c r="C267" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D267" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B268" s="8" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C268" t="s">
-        <v>2061</v>
-      </c>
-      <c r="D268" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B269" t="n">
-        <v>600</v>
-      </c>
-      <c r="C269" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B270" t="n">
-        <v>601</v>
-      </c>
-      <c r="C270" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B271" t="n">
-        <v>602</v>
-      </c>
-      <c r="C271" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B272" t="n">
-        <v>603</v>
-      </c>
-      <c r="C272" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B273" t="n">
-        <v>900</v>
-      </c>
-      <c r="C273" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B274" t="n">
-        <v>901</v>
-      </c>
-      <c r="C274" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B275" t="n">
-        <v>902</v>
-      </c>
-      <c r="C275" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B276" t="n">
-        <v>903</v>
-      </c>
-      <c r="C276" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B277" t="n">
-        <v>904</v>
-      </c>
-      <c r="C277" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D277" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B278" t="n">
-        <v>905</v>
-      </c>
-      <c r="C278" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B279" t="n">
-        <v>906</v>
-      </c>
-      <c r="C279" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B280" t="n">
-        <v>907</v>
-      </c>
-      <c r="C280" t="s">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B281" t="n">
-        <v>908</v>
-      </c>
-      <c r="C281" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B282" t="n">
-        <v>909</v>
-      </c>
-      <c r="C282" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B283" t="n">
-        <v>910</v>
-      </c>
-      <c r="C283" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B284" t="n">
-        <v>911</v>
-      </c>
-      <c r="C284" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B285" t="n">
-        <v>912</v>
-      </c>
-      <c r="C285" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B286" t="n">
-        <v>913</v>
-      </c>
-      <c r="C286" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B287" t="n">
-        <v>914</v>
-      </c>
-      <c r="C287" t="s">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B288" t="n">
-        <v>915</v>
-      </c>
-      <c r="C288" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B289" t="n">
-        <v>916</v>
-      </c>
-      <c r="C289" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B290" t="n">
-        <v>917</v>
-      </c>
-      <c r="C290" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B291" t="n">
-        <v>918</v>
-      </c>
-      <c r="C291" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B292" t="n">
-        <v>919</v>
-      </c>
-      <c r="C292" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B293" t="n">
-        <v>920</v>
-      </c>
-      <c r="C293" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B294" t="n">
-        <v>921</v>
-      </c>
-      <c r="C294" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B295" t="n">
-        <v>922</v>
-      </c>
-      <c r="C295" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B296" t="n">
-        <v>923</v>
-      </c>
-      <c r="C296" t="s">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B297" t="n">
-        <v>924</v>
-      </c>
-      <c r="C297" t="s">
-        <v>2093</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B298" t="n">
-        <v>925</v>
-      </c>
-      <c r="C298" t="s">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B299" t="n">
-        <v>926</v>
-      </c>
-      <c r="C299" t="s">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B300" t="n">
-        <v>928</v>
-      </c>
-      <c r="C300" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B301" t="n">
-        <v>930</v>
-      </c>
-      <c r="C301" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B302" t="n">
-        <v>931</v>
-      </c>
-      <c r="C302" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B303" t="n">
-        <v>990</v>
-      </c>
-      <c r="C303" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B304" t="n">
-        <v>994</v>
-      </c>
-      <c r="C304" t="s">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B305" t="n">
-        <v>995</v>
-      </c>
-      <c r="C305" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B306" t="n">
-        <v>998</v>
-      </c>
-      <c r="C306" t="s">
-        <v>2102</v>
+      <c r="B5" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20241213</v>
       </c>
     </row>
   </sheetData>
@@ -12134,60 +12050,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1671</v>
+        <v>2105</v>
       </c>
       <c r="B1" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1674</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>2107</v>
       </c>
       <c r="B2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20241213</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>2109</v>
       </c>
       <c r="B3" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20241213</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
+      <c r="A4" t="s">
+        <v>2111</v>
       </c>
       <c r="B4" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C4" t="n">
-        <v>20241213</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>0</v>
+      <c r="A5" t="s">
+        <v>2113</v>
       </c>
       <c r="B5" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C5" t="n">
-        <v>20241213</v>
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2130</v>
       </c>
     </row>
   </sheetData>
@@ -12203,106 +12165,244 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2105</v>
+        <v>2131</v>
       </c>
       <c r="B1" t="s">
-        <v>2106</v>
+        <v>2132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2133</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>2107</v>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2108</v>
+        <v>2134</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>2109</v>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2110</v>
+        <v>2135</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>2111</v>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2112</v>
+        <v>2136</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>2113</v>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2114</v>
+        <v>2137</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>2115</v>
+      <c r="A6" t="n">
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>2116</v>
+        <v>2138</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20260506</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>2117</v>
+      <c r="A7" t="n">
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>2118</v>
+        <v>2138</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20260506</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>2119</v>
+      <c r="A8" t="n">
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>2120</v>
+        <v>2139</v>
+      </c>
+      <c r="C8" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>2121</v>
+      <c r="A9" t="n">
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>2122</v>
+        <v>2140</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
-        <v>2123</v>
+      <c r="A10" t="n">
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>2124</v>
+        <v>2141</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>2125</v>
+      <c r="A11" t="n">
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>2126</v>
+        <v>2142</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
-        <v>2127</v>
+      <c r="A12" t="n">
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>2128</v>
+        <v>2143</v>
+      </c>
+      <c r="C12" t="n">
+        <v>20241213</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>2129</v>
+      <c r="A13" t="n">
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>2130</v>
+        <v>2144</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C18" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20241213</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20260506</v>
       </c>
     </row>
   </sheetData>
